--- a/Financial Analysis/PAGS.xlsx
+++ b/Financial Analysis/PAGS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CC5E3D-CF3B-4654-AD9F-852FA71AD10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62705682-10E6-4C05-9C71-F0D7FCD1C8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{59555B69-E0C6-4AC2-AD53-EB3ED27D9884}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
   <si>
     <t>PAGS</t>
   </si>
@@ -235,13 +235,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Q424 6K</t>
-  </si>
-  <si>
-    <t>Overvalued</t>
-  </si>
-  <si>
-    <t>unsure about the debt, heavily depends on it</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -400,14 +394,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -424,7 +418,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11811000" y="0"/>
+          <a:off x="13045440" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -774,17 +768,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="10">
-        <v>8.5</v>
+        <v>10.68</v>
       </c>
       <c r="E3" s="3">
-        <v>45751</v>
+        <v>45918</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45918</v>
       </c>
       <c r="G3" s="3">
-        <v>45806</v>
+        <v>45980</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -792,11 +786,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>316.1</f>
-        <v>316.10000000000002</v>
+        <f>297.7</f>
+        <v>297.7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -805,7 +799,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>2686.8500000000004</v>
+        <v>3179.4359999999997</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -813,11 +807,11 @@
         <v>9</v>
       </c>
       <c r="D6" s="4">
-        <f>927.7+487.9</f>
-        <v>1415.6</v>
+        <f>1128.2+448</f>
+        <v>1576.2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -825,11 +819,11 @@
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <f>4521.5+7050.7</f>
-        <v>11572.2</v>
+        <f>3448.5</f>
+        <v>3448.5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -838,7 +832,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6/D13</f>
-        <v>248.35087719298244</v>
+        <v>279.468085106383</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,7 +841,7 @@
       </c>
       <c r="D9" s="4">
         <f>D7/D13</f>
-        <v>2030.2105263157896</v>
+        <v>611.436170212766</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
@@ -856,7 +850,7 @@
       </c>
       <c r="D10" s="4">
         <f>D8-D9</f>
-        <v>-1781.8596491228072</v>
+        <v>-331.968085106383</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
@@ -865,7 +859,7 @@
       </c>
       <c r="D11" s="4">
         <f>D5-D10</f>
-        <v>4468.7096491228076</v>
+        <v>3511.4040851063828</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
@@ -873,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="5">
-        <v>5.7</v>
+        <v>5.64</v>
       </c>
     </row>
   </sheetData>
@@ -883,13 +877,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7320E34A-0DF9-4B4E-942B-EABFE6EEF5C0}">
-  <dimension ref="B2:ET32"/>
+  <dimension ref="B2:ET30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
     <col min="44" max="44" width="13.21875" customWidth="1"/>
-    <col min="45" max="45" width="14.109375" customWidth="1"/>
+    <col min="45" max="45" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:150" x14ac:dyDescent="0.3">
@@ -1057,20 +1051,18 @@
         <v>2242</v>
       </c>
       <c r="S3" s="4">
-        <f>O3*1.02</f>
-        <v>2416.788</v>
+        <v>2013.9</v>
       </c>
       <c r="T3" s="4">
-        <f t="shared" ref="T3:V3" si="0">P3*1.02</f>
-        <v>2358.2400000000002</v>
+        <v>1988.7</v>
       </c>
       <c r="U3" s="4">
-        <f t="shared" si="0"/>
-        <v>2305.098</v>
+        <f>Q3*0.88</f>
+        <v>1988.712</v>
       </c>
       <c r="V3" s="4">
-        <f t="shared" si="0"/>
-        <v>2286.84</v>
+        <f>R3*0.89</f>
+        <v>1995.38</v>
       </c>
       <c r="X3" s="4">
         <f>2267.1+374.6</f>
@@ -1098,47 +1090,47 @@
       </c>
       <c r="AE3" s="4">
         <f>SUM(S3:V3)</f>
-        <v>9366.9660000000003</v>
+        <v>7986.692</v>
       </c>
       <c r="AF3" s="4">
-        <f>AE3*1.02</f>
-        <v>9554.3053200000013</v>
+        <f>AE3*0.95</f>
+        <v>7587.3573999999999</v>
       </c>
       <c r="AG3" s="4">
         <f>AF3*1.02</f>
-        <v>9745.3914264000014</v>
+        <v>7739.1045480000002</v>
       </c>
       <c r="AH3" s="4">
         <f>AG3*1.02</f>
-        <v>9940.2992549280007</v>
+        <v>7893.8866389600007</v>
       </c>
       <c r="AI3" s="4">
         <f>AH3*1.02</f>
-        <v>10139.105240026562</v>
+        <v>8051.7643717392011</v>
       </c>
       <c r="AJ3" s="4">
         <f>AI3*1.01</f>
-        <v>10240.496292426827</v>
+        <v>8132.2820154565934</v>
       </c>
       <c r="AK3" s="4">
-        <f t="shared" ref="AK3:AO3" si="1">AJ3*1.01</f>
-        <v>10342.901255351097</v>
+        <f t="shared" ref="AK3:AO3" si="0">AJ3*1.01</f>
+        <v>8213.6048356111587</v>
       </c>
       <c r="AL3" s="4">
-        <f t="shared" si="1"/>
-        <v>10446.330267904608</v>
+        <f t="shared" si="0"/>
+        <v>8295.7408839672698</v>
       </c>
       <c r="AM3" s="4">
-        <f t="shared" si="1"/>
-        <v>10550.793570583655</v>
+        <f t="shared" si="0"/>
+        <v>8378.6982928069428</v>
       </c>
       <c r="AN3" s="4">
-        <f t="shared" si="1"/>
-        <v>10656.301506289492</v>
+        <f t="shared" si="0"/>
+        <v>8462.4852757350127</v>
       </c>
       <c r="AO3" s="4">
-        <f t="shared" si="1"/>
-        <v>10762.864521352387</v>
+        <f t="shared" si="0"/>
+        <v>8547.1101284923625</v>
       </c>
     </row>
     <row r="4" spans="2:150" x14ac:dyDescent="0.3">
@@ -1190,12 +1182,10 @@
         <v>2761</v>
       </c>
       <c r="S4" s="4">
-        <f>O4*1.4</f>
-        <v>2564.7999999999997</v>
+        <v>2697.3</v>
       </c>
       <c r="T4" s="4">
-        <f t="shared" ref="T4" si="2">P4*1.4</f>
-        <v>2958.3399999999997</v>
+        <v>2902.3</v>
       </c>
       <c r="U4" s="4">
         <f>Q4*1.3</f>
@@ -1229,47 +1219,47 @@
       </c>
       <c r="AE4" s="4">
         <f>SUM(S4:V4)</f>
-        <v>12014.579999999998</v>
+        <v>12091.04</v>
       </c>
       <c r="AF4" s="4">
-        <f>AE4*1.15</f>
-        <v>13816.766999999996</v>
+        <f>AE4*1.16</f>
+        <v>14025.606400000001</v>
       </c>
       <c r="AG4" s="4">
         <f>AF4*1.08</f>
-        <v>14922.108359999997</v>
+        <v>15147.654912000002</v>
       </c>
       <c r="AH4" s="4">
         <f>AG4*1.05</f>
-        <v>15668.213777999998</v>
+        <v>15905.037657600002</v>
       </c>
       <c r="AI4" s="4">
         <f>AH4*1.04</f>
-        <v>16294.942329119998</v>
+        <v>16541.239163904003</v>
       </c>
       <c r="AJ4" s="4">
         <f>AI4*1.03</f>
-        <v>16783.790598993597</v>
+        <v>17037.476338821125</v>
       </c>
       <c r="AK4" s="4">
         <f>AJ4*1.02</f>
-        <v>17119.466410973469</v>
+        <v>17378.225865597549</v>
       </c>
       <c r="AL4" s="4">
-        <f t="shared" ref="AL4:AO4" si="3">AK4*1.01</f>
-        <v>17290.661075083204</v>
+        <f t="shared" ref="AL4:AO4" si="1">AK4*1.01</f>
+        <v>17552.008124253523</v>
       </c>
       <c r="AM4" s="4">
-        <f t="shared" si="3"/>
-        <v>17463.567685834038</v>
+        <f t="shared" si="1"/>
+        <v>17727.528205496059</v>
       </c>
       <c r="AN4" s="4">
-        <f t="shared" si="3"/>
-        <v>17638.203362692377</v>
+        <f t="shared" si="1"/>
+        <v>17904.80348755102</v>
       </c>
       <c r="AO4" s="4">
-        <f t="shared" si="3"/>
-        <v>17814.5853963193</v>
+        <f t="shared" si="1"/>
+        <v>18083.851522426532</v>
       </c>
     </row>
     <row r="5" spans="2:150" x14ac:dyDescent="0.3">
@@ -1321,16 +1311,14 @@
         <v>112</v>
       </c>
       <c r="S5" s="4">
-        <f>O5*1.5</f>
-        <v>157.64999999999998</v>
+        <v>138.9</v>
       </c>
       <c r="T5" s="4">
-        <f>P5*1.4</f>
-        <v>184.37999999999997</v>
+        <v>167.2</v>
       </c>
       <c r="U5" s="4">
-        <f t="shared" ref="U5" si="4">Q5*1.5</f>
-        <v>190.2</v>
+        <f>Q5*1.28</f>
+        <v>162.304</v>
       </c>
       <c r="V5" s="4">
         <f>R5*1.3</f>
@@ -1360,47 +1348,47 @@
       </c>
       <c r="AE5" s="4">
         <f>SUM(S5:V5)</f>
-        <v>677.83</v>
+        <v>614.00400000000002</v>
       </c>
       <c r="AF5" s="4">
-        <f>AE5*1.35</f>
-        <v>915.07050000000015</v>
+        <f>AE5*1.2</f>
+        <v>736.8048</v>
       </c>
       <c r="AG5" s="4">
-        <f>AF5*1.3</f>
-        <v>1189.5916500000003</v>
+        <f>AF5*1.15</f>
+        <v>847.32551999999998</v>
       </c>
       <c r="AH5" s="4">
-        <f>AG5*1.2</f>
-        <v>1427.5099800000003</v>
+        <f>AG5*1.1</f>
+        <v>932.05807200000004</v>
       </c>
       <c r="AI5" s="4">
-        <f>AH5*1.15</f>
-        <v>1641.6364770000002</v>
+        <f>AH5*1.05</f>
+        <v>978.66097560000003</v>
       </c>
       <c r="AJ5" s="4">
-        <f>AI5*1.09</f>
-        <v>1789.3837599300005</v>
+        <f>AI5*1.04</f>
+        <v>1017.8074146240001</v>
       </c>
       <c r="AK5" s="4">
-        <f>AJ5*1.07</f>
-        <v>1914.6406231251005</v>
+        <f>AJ5*1.03</f>
+        <v>1048.3416370627201</v>
       </c>
       <c r="AL5" s="4">
-        <f>AK5*1.05</f>
-        <v>2010.3726542813556</v>
+        <f t="shared" ref="AL5:AO5" si="2">AK5*1.03</f>
+        <v>1079.7918861746018</v>
       </c>
       <c r="AM5" s="4">
-        <f>AL5*1.04</f>
-        <v>2090.7875604526098</v>
+        <f t="shared" si="2"/>
+        <v>1112.18564275984</v>
       </c>
       <c r="AN5" s="4">
-        <f>AM5*1.03</f>
-        <v>2153.5111872661882</v>
+        <f t="shared" si="2"/>
+        <v>1145.5512120426351</v>
       </c>
       <c r="AO5" s="4">
-        <f t="shared" ref="AO5" si="5">AN5*1.02</f>
-        <v>2196.581411011512</v>
+        <f t="shared" si="2"/>
+        <v>1179.9177484039142</v>
       </c>
     </row>
     <row r="6" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1416,140 +1404,140 @@
         <v>2369.6</v>
       </c>
       <c r="G6" s="8">
-        <f t="shared" ref="G6:P6" si="6">SUM(G3:G5)</f>
+        <f t="shared" ref="G6:P6" si="3">SUM(G3:G5)</f>
         <v>3426.9999999999995</v>
       </c>
       <c r="H6" s="8">
+        <f t="shared" si="3"/>
+        <v>3910.6</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="3"/>
+        <v>4035.4</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" si="3"/>
+        <v>3961.8999999999996</v>
+      </c>
+      <c r="K6" s="8">
+        <f t="shared" si="3"/>
+        <v>3749.7</v>
+      </c>
+      <c r="L6" s="8">
+        <f t="shared" si="3"/>
+        <v>3825.9</v>
+      </c>
+      <c r="M6" s="8">
+        <f t="shared" si="3"/>
+        <v>4026.2000000000003</v>
+      </c>
+      <c r="N6" s="8">
+        <f t="shared" si="3"/>
+        <v>4346.5000000000009</v>
+      </c>
+      <c r="O6" s="8">
+        <f t="shared" si="3"/>
+        <v>4306.5</v>
+      </c>
+      <c r="P6" s="8">
+        <f t="shared" si="3"/>
+        <v>4556.8</v>
+      </c>
+      <c r="Q6" s="8">
+        <f t="shared" ref="Q6:V6" si="4">SUM(Q3:Q5)</f>
+        <v>4831.5000000000009</v>
+      </c>
+      <c r="R6" s="8">
+        <f t="shared" si="4"/>
+        <v>5115</v>
+      </c>
+      <c r="S6" s="8">
+        <f t="shared" si="4"/>
+        <v>4850.1000000000004</v>
+      </c>
+      <c r="T6" s="8">
+        <f t="shared" si="4"/>
+        <v>5058.2</v>
+      </c>
+      <c r="U6" s="8">
+        <f t="shared" si="4"/>
+        <v>5329.2560000000003</v>
+      </c>
+      <c r="V6" s="8">
+        <f t="shared" si="4"/>
+        <v>5454.18</v>
+      </c>
+      <c r="X6" s="8">
+        <f t="shared" ref="X6:AD6" si="5">SUM(X3:X5)</f>
+        <v>4334.5999999999995</v>
+      </c>
+      <c r="Y6" s="8">
+        <f t="shared" si="5"/>
+        <v>5707.1999999999989</v>
+      </c>
+      <c r="Z6" s="8">
+        <f t="shared" si="5"/>
+        <v>6814.7000000000007</v>
+      </c>
+      <c r="AA6" s="8">
+        <f t="shared" si="5"/>
+        <v>10448.700000000001</v>
+      </c>
+      <c r="AB6" s="8">
+        <f t="shared" si="5"/>
+        <v>15334.899999999998</v>
+      </c>
+      <c r="AC6" s="8">
+        <f t="shared" si="5"/>
+        <v>15948.300000000001</v>
+      </c>
+      <c r="AD6" s="8">
+        <f t="shared" si="5"/>
+        <v>18809.799999999996</v>
+      </c>
+      <c r="AE6" s="8">
+        <f t="shared" ref="AE6:AO6" si="6">SUM(AE3:AE5)</f>
+        <v>20691.736000000001</v>
+      </c>
+      <c r="AF6" s="8">
         <f t="shared" si="6"/>
-        <v>3910.6</v>
-      </c>
-      <c r="I6" s="8">
+        <v>22349.768600000003</v>
+      </c>
+      <c r="AG6" s="8">
         <f t="shared" si="6"/>
-        <v>4035.4</v>
-      </c>
-      <c r="J6" s="8">
+        <v>23734.08498</v>
+      </c>
+      <c r="AH6" s="8">
         <f t="shared" si="6"/>
-        <v>3961.8999999999996</v>
-      </c>
-      <c r="K6" s="8">
+        <v>24730.982368560002</v>
+      </c>
+      <c r="AI6" s="8">
         <f t="shared" si="6"/>
-        <v>3749.7</v>
-      </c>
-      <c r="L6" s="8">
+        <v>25571.664511243205</v>
+      </c>
+      <c r="AJ6" s="8">
         <f t="shared" si="6"/>
-        <v>3825.9</v>
-      </c>
-      <c r="M6" s="8">
+        <v>26187.565768901717</v>
+      </c>
+      <c r="AK6" s="8">
         <f t="shared" si="6"/>
-        <v>4026.2000000000003</v>
-      </c>
-      <c r="N6" s="8">
+        <v>26640.17233827143</v>
+      </c>
+      <c r="AL6" s="8">
         <f t="shared" si="6"/>
-        <v>4346.5000000000009</v>
-      </c>
-      <c r="O6" s="8">
+        <v>26927.540894395395</v>
+      </c>
+      <c r="AM6" s="8">
         <f t="shared" si="6"/>
-        <v>4306.5</v>
-      </c>
-      <c r="P6" s="8">
+        <v>27218.412141062843</v>
+      </c>
+      <c r="AN6" s="8">
         <f t="shared" si="6"/>
-        <v>4556.8</v>
-      </c>
-      <c r="Q6" s="8">
-        <f t="shared" ref="Q6:V6" si="7">SUM(Q3:Q5)</f>
-        <v>4831.5000000000009</v>
-      </c>
-      <c r="R6" s="8">
-        <f t="shared" si="7"/>
-        <v>5115</v>
-      </c>
-      <c r="S6" s="8">
-        <f t="shared" si="7"/>
-        <v>5139.2379999999994</v>
-      </c>
-      <c r="T6" s="8">
-        <f t="shared" si="7"/>
-        <v>5500.96</v>
-      </c>
-      <c r="U6" s="8">
-        <f t="shared" si="7"/>
-        <v>5673.5379999999996</v>
-      </c>
-      <c r="V6" s="8">
-        <f t="shared" si="7"/>
-        <v>5745.64</v>
-      </c>
-      <c r="X6" s="8">
-        <f t="shared" ref="X6:AD6" si="8">SUM(X3:X5)</f>
-        <v>4334.5999999999995</v>
-      </c>
-      <c r="Y6" s="8">
-        <f t="shared" si="8"/>
-        <v>5707.1999999999989</v>
-      </c>
-      <c r="Z6" s="8">
-        <f t="shared" si="8"/>
-        <v>6814.7000000000007</v>
-      </c>
-      <c r="AA6" s="8">
-        <f t="shared" si="8"/>
-        <v>10448.700000000001</v>
-      </c>
-      <c r="AB6" s="8">
-        <f t="shared" si="8"/>
-        <v>15334.899999999998</v>
-      </c>
-      <c r="AC6" s="8">
-        <f t="shared" si="8"/>
-        <v>15948.300000000001</v>
-      </c>
-      <c r="AD6" s="8">
-        <f t="shared" si="8"/>
-        <v>18809.799999999996</v>
-      </c>
-      <c r="AE6" s="8">
-        <f t="shared" ref="AE6:AO6" si="9">SUM(AE3:AE5)</f>
-        <v>22059.376</v>
-      </c>
-      <c r="AF6" s="8">
-        <f t="shared" si="9"/>
-        <v>24286.142820000001</v>
-      </c>
-      <c r="AG6" s="8">
-        <f t="shared" si="9"/>
-        <v>25857.091436399998</v>
-      </c>
-      <c r="AH6" s="8">
-        <f t="shared" si="9"/>
-        <v>27036.023012927999</v>
-      </c>
-      <c r="AI6" s="8">
-        <f t="shared" si="9"/>
-        <v>28075.684046146562</v>
-      </c>
-      <c r="AJ6" s="8">
-        <f t="shared" si="9"/>
-        <v>28813.670651350425</v>
-      </c>
-      <c r="AK6" s="8">
-        <f t="shared" si="9"/>
-        <v>29377.008289449666</v>
-      </c>
-      <c r="AL6" s="8">
-        <f t="shared" si="9"/>
-        <v>29747.363997269171</v>
-      </c>
-      <c r="AM6" s="8">
-        <f t="shared" si="9"/>
-        <v>30105.148816870304</v>
-      </c>
-      <c r="AN6" s="8">
-        <f t="shared" si="9"/>
-        <v>30448.016056248056</v>
+        <v>27512.839975328669</v>
       </c>
       <c r="AO6" s="8">
-        <f t="shared" si="9"/>
-        <v>30774.031328683199</v>
+        <f t="shared" si="6"/>
+        <v>27810.879399322806</v>
       </c>
     </row>
     <row r="7" spans="2:150" x14ac:dyDescent="0.3">
@@ -1601,20 +1589,18 @@
         <v>2585</v>
       </c>
       <c r="S7" s="4">
-        <f>S6-S8</f>
-        <v>2569.6189999999997</v>
+        <v>2360.1999999999998</v>
       </c>
       <c r="T7" s="4">
-        <f t="shared" ref="T7:V7" si="10">T6-T8</f>
-        <v>2750.48</v>
+        <v>2410.8000000000002</v>
       </c>
       <c r="U7" s="4">
-        <f t="shared" si="10"/>
-        <v>2893.5043799999999</v>
+        <f t="shared" ref="U7:V7" si="7">U6-U8</f>
+        <v>2611.3354400000003</v>
       </c>
       <c r="V7" s="4">
-        <f t="shared" si="10"/>
-        <v>2987.7328000000002</v>
+        <f t="shared" si="7"/>
+        <v>2618.0064000000002</v>
       </c>
       <c r="X7" s="4">
         <v>2144.6999999999998</v>
@@ -1640,47 +1626,47 @@
       </c>
       <c r="AE7" s="4">
         <f>SUM(S7:V7)</f>
-        <v>11201.33618</v>
+        <v>10000.341840000001</v>
       </c>
       <c r="AF7" s="4">
-        <f t="shared" ref="AF7:AO7" si="11">AF6-AF8</f>
-        <v>12385.9328382</v>
+        <f t="shared" ref="AF7:AO7" si="8">AF6-AF8</f>
+        <v>10504.391242000002</v>
       </c>
       <c r="AG7" s="4">
-        <f t="shared" si="11"/>
-        <v>13187.116632563999</v>
+        <f t="shared" si="8"/>
+        <v>10917.679090799998</v>
       </c>
       <c r="AH7" s="4">
-        <f t="shared" si="11"/>
-        <v>13788.371736593279</v>
+        <f t="shared" si="8"/>
+        <v>11376.2518895376</v>
       </c>
       <c r="AI7" s="4">
-        <f t="shared" si="11"/>
-        <v>14318.598863534748</v>
+        <f t="shared" si="8"/>
+        <v>11762.965675171874</v>
       </c>
       <c r="AJ7" s="4">
-        <f t="shared" si="11"/>
-        <v>14694.972032188716</v>
+        <f t="shared" si="8"/>
+        <v>12046.280253694789</v>
       </c>
       <c r="AK7" s="4">
-        <f t="shared" si="11"/>
-        <v>14982.274227619329</v>
+        <f t="shared" si="8"/>
+        <v>12254.479275604857</v>
       </c>
       <c r="AL7" s="4">
-        <f t="shared" si="11"/>
-        <v>15171.155638607277</v>
+        <f t="shared" si="8"/>
+        <v>12386.668811421881</v>
       </c>
       <c r="AM7" s="4">
-        <f t="shared" si="11"/>
-        <v>15353.625896603855</v>
+        <f t="shared" si="8"/>
+        <v>12520.469584888908</v>
       </c>
       <c r="AN7" s="4">
-        <f t="shared" si="11"/>
-        <v>15528.48818868651</v>
+        <f t="shared" si="8"/>
+        <v>12655.906388651187</v>
       </c>
       <c r="AO7" s="4">
-        <f t="shared" si="11"/>
-        <v>15694.755977628432</v>
+        <f t="shared" si="8"/>
+        <v>12793.004523688491</v>
       </c>
     </row>
     <row r="8" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1696,140 +1682,140 @@
         <v>1074.5</v>
       </c>
       <c r="G8" s="8">
-        <f t="shared" ref="G8:Q8" si="12">G6-G7</f>
+        <f t="shared" ref="G8:T8" si="9">G6-G7</f>
         <v>1687.5999999999995</v>
       </c>
       <c r="H8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2010.3</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2173.1999999999998</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1992.9</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1820.3999999999999</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1899.8000000000002</v>
       </c>
       <c r="M8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1992.9000000000003</v>
       </c>
       <c r="N8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2102.6000000000004</v>
       </c>
       <c r="O8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2135.8000000000002</v>
       </c>
       <c r="P8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2224.6000000000004</v>
       </c>
       <c r="Q8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2376.1000000000008</v>
       </c>
       <c r="R8" s="8">
-        <f>R6*0.48</f>
-        <v>2455.1999999999998</v>
+        <f t="shared" si="9"/>
+        <v>2530</v>
       </c>
       <c r="S8" s="8">
-        <f>S6*0.5</f>
-        <v>2569.6189999999997</v>
+        <f t="shared" si="9"/>
+        <v>2489.9000000000005</v>
       </c>
       <c r="T8" s="8">
-        <f t="shared" ref="T8" si="13">T6*0.5</f>
-        <v>2750.48</v>
+        <f t="shared" si="9"/>
+        <v>2647.3999999999996</v>
       </c>
       <c r="U8" s="8">
-        <f>U6*0.49</f>
-        <v>2780.0336199999997</v>
+        <f>U6*0.51</f>
+        <v>2717.92056</v>
       </c>
       <c r="V8" s="8">
-        <f>V6*0.48</f>
-        <v>2757.9072000000001</v>
+        <f>V6*0.52</f>
+        <v>2836.1736000000001</v>
       </c>
       <c r="X8" s="8">
-        <f t="shared" ref="X8:AE8" si="14">X6-X7</f>
+        <f t="shared" ref="X8:AE8" si="10">X6-X7</f>
         <v>2189.8999999999996</v>
       </c>
       <c r="Y8" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>2945.099999999999</v>
       </c>
       <c r="Z8" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>3042.4000000000005</v>
       </c>
       <c r="AA8" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>4672.8000000000011</v>
       </c>
       <c r="AB8" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>7863.9999999999982</v>
       </c>
       <c r="AC8" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>7815.7000000000007</v>
       </c>
       <c r="AD8" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>9266.4999999999964</v>
       </c>
       <c r="AE8" s="8">
-        <f t="shared" si="14"/>
-        <v>10858.03982</v>
+        <f t="shared" si="10"/>
+        <v>10691.39416</v>
       </c>
       <c r="AF8" s="8">
-        <f t="shared" ref="AF8:AO8" si="15">AF6*0.49</f>
-        <v>11900.209981800001</v>
+        <f>AF6*0.53</f>
+        <v>11845.377358000002</v>
       </c>
       <c r="AG8" s="8">
-        <f t="shared" si="15"/>
-        <v>12669.974803835999</v>
+        <f>AG6*0.54</f>
+        <v>12816.405889200001</v>
       </c>
       <c r="AH8" s="8">
-        <f t="shared" si="15"/>
-        <v>13247.65127633472</v>
+        <f t="shared" ref="AH8:AO8" si="11">AH6*0.54</f>
+        <v>13354.730479022403</v>
       </c>
       <c r="AI8" s="8">
-        <f t="shared" si="15"/>
-        <v>13757.085182611814</v>
+        <f t="shared" si="11"/>
+        <v>13808.698836071331</v>
       </c>
       <c r="AJ8" s="8">
-        <f t="shared" si="15"/>
-        <v>14118.698619161709</v>
+        <f t="shared" si="11"/>
+        <v>14141.285515206928</v>
       </c>
       <c r="AK8" s="8">
-        <f t="shared" si="15"/>
-        <v>14394.734061830337</v>
+        <f t="shared" si="11"/>
+        <v>14385.693062666573</v>
       </c>
       <c r="AL8" s="8">
-        <f t="shared" si="15"/>
-        <v>14576.208358661894</v>
+        <f t="shared" si="11"/>
+        <v>14540.872082973514</v>
       </c>
       <c r="AM8" s="8">
-        <f t="shared" si="15"/>
-        <v>14751.522920266449</v>
+        <f t="shared" si="11"/>
+        <v>14697.942556173935</v>
       </c>
       <c r="AN8" s="8">
-        <f t="shared" si="15"/>
-        <v>14919.527867561546</v>
+        <f t="shared" si="11"/>
+        <v>14856.933586677482</v>
       </c>
       <c r="AO8" s="8">
-        <f t="shared" si="15"/>
-        <v>15079.275351054766</v>
+        <f t="shared" si="11"/>
+        <v>15017.874875634316</v>
       </c>
     </row>
     <row r="9" spans="2:150" x14ac:dyDescent="0.3">
@@ -1881,20 +1867,18 @@
         <v>468</v>
       </c>
       <c r="S9" s="4">
-        <f>S6*0.1</f>
-        <v>513.92379999999991</v>
+        <v>423.1</v>
       </c>
       <c r="T9" s="4">
-        <f t="shared" ref="T9:U9" si="16">T6*0.1</f>
-        <v>550.096</v>
+        <v>452.4</v>
       </c>
       <c r="U9" s="4">
-        <f t="shared" si="16"/>
-        <v>567.35379999999998</v>
+        <f>U6*0.09</f>
+        <v>479.63303999999999</v>
       </c>
       <c r="V9" s="4">
         <f>V6*0.09</f>
-        <v>517.10760000000005</v>
+        <v>490.87619999999998</v>
       </c>
       <c r="X9" s="4">
         <v>351.4</v>
@@ -1920,47 +1904,47 @@
       </c>
       <c r="AE9" s="4">
         <f>SUM(S9:V9)</f>
-        <v>2148.4812000000002</v>
+        <v>1846.0092399999999</v>
       </c>
       <c r="AF9" s="4">
-        <f t="shared" ref="AF9:AO9" si="17">AF6*0.1</f>
-        <v>2428.614282</v>
+        <f>AF6*0.09</f>
+        <v>2011.4791740000003</v>
       </c>
       <c r="AG9" s="4">
-        <f t="shared" si="17"/>
-        <v>2585.7091436400001</v>
+        <f t="shared" ref="AG9:AO9" si="12">AG6*0.09</f>
+        <v>2136.0676481999999</v>
       </c>
       <c r="AH9" s="4">
-        <f t="shared" si="17"/>
-        <v>2703.6023012927999</v>
+        <f t="shared" si="12"/>
+        <v>2225.7884131704</v>
       </c>
       <c r="AI9" s="4">
-        <f t="shared" si="17"/>
-        <v>2807.5684046146562</v>
+        <f t="shared" si="12"/>
+        <v>2301.4498060118885</v>
       </c>
       <c r="AJ9" s="4">
-        <f t="shared" si="17"/>
-        <v>2881.3670651350426</v>
+        <f t="shared" si="12"/>
+        <v>2356.8809192011545</v>
       </c>
       <c r="AK9" s="4">
-        <f t="shared" si="17"/>
-        <v>2937.7008289449668</v>
+        <f t="shared" si="12"/>
+        <v>2397.6155104444288</v>
       </c>
       <c r="AL9" s="4">
-        <f t="shared" si="17"/>
-        <v>2974.7363997269172</v>
+        <f t="shared" si="12"/>
+        <v>2423.4786804955856</v>
       </c>
       <c r="AM9" s="4">
-        <f t="shared" si="17"/>
-        <v>3010.5148816870305</v>
+        <f t="shared" si="12"/>
+        <v>2449.6570926956556</v>
       </c>
       <c r="AN9" s="4">
-        <f t="shared" si="17"/>
-        <v>3044.8016056248057</v>
+        <f t="shared" si="12"/>
+        <v>2476.1555977795801</v>
       </c>
       <c r="AO9" s="4">
-        <f t="shared" si="17"/>
-        <v>3077.40313286832</v>
+        <f t="shared" si="12"/>
+        <v>2502.9791459390526</v>
       </c>
     </row>
     <row r="10" spans="2:150" x14ac:dyDescent="0.3">
@@ -2012,20 +1996,18 @@
         <v>257</v>
       </c>
       <c r="S10" s="4">
-        <f>O10*1.3</f>
-        <v>299.78000000000003</v>
+        <v>242.9</v>
       </c>
       <c r="T10" s="4">
-        <f t="shared" ref="T10" si="18">P10*1.5</f>
-        <v>324.29999999999995</v>
+        <v>226.7</v>
       </c>
       <c r="U10" s="4">
-        <f>Q10*1.3</f>
-        <v>349.05</v>
+        <f>Q10*1.05</f>
+        <v>281.92500000000001</v>
       </c>
       <c r="V10" s="4">
-        <f>R10*1.3</f>
-        <v>334.1</v>
+        <f>R10*1.15</f>
+        <v>295.54999999999995</v>
       </c>
       <c r="X10" s="4">
         <v>581.70000000000005</v>
@@ -2051,47 +2033,47 @@
       </c>
       <c r="AE10" s="4">
         <f>SUM(S10:V10)</f>
-        <v>1307.23</v>
+        <v>1047.075</v>
       </c>
       <c r="AF10" s="4">
-        <f>AE10*1.2</f>
-        <v>1568.6759999999999</v>
+        <f>AE10*1.06</f>
+        <v>1109.8995000000002</v>
       </c>
       <c r="AG10" s="4">
-        <f>AF10*1.1</f>
-        <v>1725.5436</v>
+        <f>AF10*1.04</f>
+        <v>1154.2954800000002</v>
       </c>
       <c r="AH10" s="4">
-        <f>AG10*1.05</f>
-        <v>1811.82078</v>
+        <f>AG10*1.03</f>
+        <v>1188.9243444000003</v>
       </c>
       <c r="AI10" s="4">
-        <f>AH10*1.04</f>
-        <v>1884.2936112</v>
+        <f>AH10*1.02</f>
+        <v>1212.7028312880004</v>
       </c>
       <c r="AJ10" s="4">
-        <f>AI10*1.03</f>
-        <v>1940.8224195360001</v>
+        <f>AI10*1.02</f>
+        <v>1236.9568879137605</v>
       </c>
       <c r="AK10" s="4">
-        <f t="shared" ref="AK10:AO10" si="19">AJ10*1.02</f>
-        <v>1979.6388679267202</v>
+        <f>AJ10*1.01</f>
+        <v>1249.3264567928982</v>
       </c>
       <c r="AL10" s="4">
-        <f t="shared" si="19"/>
-        <v>2019.2316452852547</v>
+        <f t="shared" ref="AL10:AO10" si="13">AK10*1.01</f>
+        <v>1261.8197213608271</v>
       </c>
       <c r="AM10" s="4">
-        <f t="shared" si="19"/>
-        <v>2059.6162781909597</v>
+        <f t="shared" si="13"/>
+        <v>1274.4379185744353</v>
       </c>
       <c r="AN10" s="4">
-        <f t="shared" si="19"/>
-        <v>2100.8086037547791</v>
+        <f t="shared" si="13"/>
+        <v>1287.1822977601796</v>
       </c>
       <c r="AO10" s="4">
-        <f t="shared" si="19"/>
-        <v>2142.8247758298749</v>
+        <f t="shared" si="13"/>
+        <v>1300.0541207377814</v>
       </c>
     </row>
     <row r="11" spans="2:150" x14ac:dyDescent="0.3">
@@ -2143,20 +2125,18 @@
         <v>1092</v>
       </c>
       <c r="S11" s="4">
-        <f>O11*1.15</f>
-        <v>951.16499999999996</v>
+        <v>1177.8</v>
       </c>
       <c r="T11" s="4">
-        <f>P11*1.15</f>
-        <v>992.90999999999985</v>
+        <v>1279.5</v>
       </c>
       <c r="U11" s="4">
-        <f>Q11*1.05</f>
-        <v>1012.515</v>
+        <f>Q11*1.4</f>
+        <v>1350.0199999999998</v>
       </c>
       <c r="V11" s="4">
-        <f t="shared" ref="V11" si="20">R11*1.05</f>
-        <v>1146.6000000000001</v>
+        <f>R11*1.3</f>
+        <v>1419.6000000000001</v>
       </c>
       <c r="X11" s="4">
         <v>31.2</v>
@@ -2182,47 +2162,47 @@
       </c>
       <c r="AE11" s="4">
         <f>SUM(S11:V11)</f>
-        <v>4103.1899999999996</v>
+        <v>5226.92</v>
       </c>
       <c r="AF11" s="4">
-        <f>AE11*1.05</f>
-        <v>4308.3494999999994</v>
+        <f>AE11*1.12</f>
+        <v>5854.1504000000004</v>
       </c>
       <c r="AG11" s="4">
-        <f>AF11*1.04</f>
-        <v>4480.6834799999997</v>
+        <f>AF11*1.06</f>
+        <v>6205.3994240000011</v>
       </c>
       <c r="AH11" s="4">
         <f>AG11*1.03</f>
-        <v>4615.1039843999997</v>
+        <v>6391.5614067200013</v>
       </c>
       <c r="AI11" s="4">
-        <f t="shared" ref="AI11:AO11" si="21">AH11*1.02</f>
-        <v>4707.4060640879998</v>
+        <f t="shared" ref="AI11:AJ11" si="14">AH11*1.02</f>
+        <v>6519.3926348544019</v>
       </c>
       <c r="AJ11" s="4">
-        <f t="shared" si="21"/>
-        <v>4801.5541853697596</v>
+        <f t="shared" si="14"/>
+        <v>6649.7804875514903</v>
       </c>
       <c r="AK11" s="4">
-        <f t="shared" si="21"/>
-        <v>4897.5852690771544</v>
+        <f>AJ11*1.01</f>
+        <v>6716.278292427005</v>
       </c>
       <c r="AL11" s="4">
-        <f t="shared" si="21"/>
-        <v>4995.5369744586978</v>
+        <f t="shared" ref="AL11:AO11" si="15">AK11*1.01</f>
+        <v>6783.4410753512748</v>
       </c>
       <c r="AM11" s="4">
-        <f t="shared" si="21"/>
-        <v>5095.4477139478722</v>
+        <f t="shared" si="15"/>
+        <v>6851.2754861047879</v>
       </c>
       <c r="AN11" s="4">
-        <f t="shared" si="21"/>
-        <v>5197.3566682268302</v>
+        <f t="shared" si="15"/>
+        <v>6919.7882409658359</v>
       </c>
       <c r="AO11" s="4">
-        <f t="shared" si="21"/>
-        <v>5301.3038015913671</v>
+        <f t="shared" si="15"/>
+        <v>6988.9861233754946</v>
       </c>
     </row>
     <row r="12" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2238,140 +2218,140 @@
         <v>351</v>
       </c>
       <c r="G12" s="8">
-        <f t="shared" ref="G12:P12" si="22">G8-SUM(G9:G11)</f>
+        <f t="shared" ref="G12:P12" si="16">G8-SUM(G9:G11)</f>
         <v>420.99999999999955</v>
       </c>
       <c r="H12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>551.70000000000005</v>
       </c>
       <c r="I12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>536.39999999999986</v>
       </c>
       <c r="J12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>588.50000000000045</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>518.09999999999991</v>
       </c>
       <c r="L12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>579.40000000000009</v>
       </c>
       <c r="M12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>588.50000000000023</v>
       </c>
       <c r="N12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>697.60000000000036</v>
       </c>
       <c r="O12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>640.70000000000027</v>
       </c>
       <c r="P12" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>677.70000000000027</v>
       </c>
       <c r="Q12" s="8">
-        <f t="shared" ref="Q12:V12" si="23">Q8-SUM(Q9:Q11)</f>
+        <f t="shared" ref="Q12:V12" si="17">Q8-SUM(Q9:Q11)</f>
         <v>656.30000000000086</v>
       </c>
       <c r="R12" s="8">
-        <f t="shared" si="23"/>
-        <v>638.19999999999982</v>
+        <f t="shared" si="17"/>
+        <v>713</v>
       </c>
       <c r="S12" s="8">
-        <f t="shared" si="23"/>
-        <v>804.75019999999972</v>
+        <f t="shared" si="17"/>
+        <v>646.10000000000059</v>
       </c>
       <c r="T12" s="8">
-        <f t="shared" si="23"/>
-        <v>883.17400000000021</v>
+        <f t="shared" si="17"/>
+        <v>688.79999999999973</v>
       </c>
       <c r="U12" s="8">
-        <f t="shared" si="23"/>
-        <v>851.11481999999978</v>
+        <f t="shared" si="17"/>
+        <v>606.34252000000015</v>
       </c>
       <c r="V12" s="8">
-        <f t="shared" si="23"/>
-        <v>760.09960000000001</v>
+        <f t="shared" si="17"/>
+        <v>630.14739999999983</v>
       </c>
       <c r="X12" s="8">
-        <f t="shared" ref="X12:AD12" si="24">X8-SUM(X9:X11)</f>
+        <f t="shared" ref="X12:AD12" si="18">X8-SUM(X9:X11)</f>
         <v>1225.5999999999995</v>
       </c>
       <c r="Y12" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="18"/>
         <v>1914.399999999999</v>
       </c>
       <c r="Z12" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="18"/>
         <v>1751.8000000000004</v>
       </c>
       <c r="AA12" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="18"/>
         <v>1480.7000000000012</v>
       </c>
       <c r="AB12" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="18"/>
         <v>2097.5999999999985</v>
       </c>
       <c r="AC12" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="18"/>
         <v>2383.6000000000004</v>
       </c>
       <c r="AD12" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="18"/>
         <v>2687.6999999999962</v>
       </c>
       <c r="AE12" s="8">
-        <f t="shared" ref="AE12:AO12" si="25">AE8-SUM(AE9:AE11)</f>
-        <v>3299.1386199999997</v>
+        <f t="shared" ref="AE12:AO12" si="19">AE8-SUM(AE9:AE11)</f>
+        <v>2571.3899199999996</v>
       </c>
       <c r="AF12" s="8">
-        <f t="shared" si="25"/>
-        <v>3594.5701998000022</v>
+        <f t="shared" si="19"/>
+        <v>2869.8482839999997</v>
       </c>
       <c r="AG12" s="8">
-        <f t="shared" si="25"/>
-        <v>3878.0385801960001</v>
+        <f t="shared" si="19"/>
+        <v>3320.6433369999995</v>
       </c>
       <c r="AH12" s="8">
-        <f t="shared" si="25"/>
-        <v>4117.1242106419195</v>
+        <f t="shared" si="19"/>
+        <v>3548.4563147320005</v>
       </c>
       <c r="AI12" s="8">
-        <f t="shared" si="25"/>
-        <v>4357.8171027091576</v>
+        <f t="shared" si="19"/>
+        <v>3775.1535639170415</v>
       </c>
       <c r="AJ12" s="8">
-        <f t="shared" si="25"/>
-        <v>4494.9549491209054</v>
+        <f t="shared" si="19"/>
+        <v>3897.667220540523</v>
       </c>
       <c r="AK12" s="8">
-        <f t="shared" si="25"/>
-        <v>4579.8090958814955</v>
+        <f t="shared" si="19"/>
+        <v>4022.4728030022397</v>
       </c>
       <c r="AL12" s="8">
-        <f t="shared" si="25"/>
-        <v>4586.7033391910227</v>
+        <f t="shared" si="19"/>
+        <v>4072.1326057658262</v>
       </c>
       <c r="AM12" s="8">
-        <f t="shared" si="25"/>
-        <v>4585.9440464405852</v>
+        <f t="shared" si="19"/>
+        <v>4122.5720587990563</v>
       </c>
       <c r="AN12" s="8">
-        <f t="shared" si="25"/>
-        <v>4576.5609899551309</v>
+        <f t="shared" si="19"/>
+        <v>4173.8074501718856</v>
       </c>
       <c r="AO12" s="8">
-        <f t="shared" si="25"/>
-        <v>4557.7436407652058</v>
+        <f t="shared" si="19"/>
+        <v>4225.8554855819875</v>
       </c>
     </row>
     <row r="13" spans="2:150" x14ac:dyDescent="0.3">
@@ -2423,19 +2403,17 @@
         <v>77</v>
       </c>
       <c r="S13" s="4">
-        <f>O13*1.02</f>
-        <v>69.564000000000007</v>
+        <v>66.2</v>
       </c>
       <c r="T13" s="4">
-        <f t="shared" ref="T13:V13" si="26">P13*1.02</f>
-        <v>101.89800000000001</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="U13" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="U13:V13" si="20">Q13*1.02</f>
         <v>64.055999999999997</v>
       </c>
       <c r="V13" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>78.540000000000006</v>
       </c>
       <c r="X13" s="4">
@@ -2462,47 +2440,47 @@
       </c>
       <c r="AE13" s="4">
         <f>SUM(S13:V13)</f>
-        <v>314.05800000000005</v>
+        <v>281.39600000000002</v>
       </c>
       <c r="AF13" s="4">
-        <f t="shared" ref="AF13:AO13" si="27">AE13*1.03</f>
-        <v>323.47974000000005</v>
+        <f t="shared" ref="AF13:AO13" si="21">AE13*1.03</f>
+        <v>289.83788000000004</v>
       </c>
       <c r="AG13" s="4">
-        <f t="shared" si="27"/>
-        <v>333.18413220000008</v>
+        <f t="shared" si="21"/>
+        <v>298.53301640000007</v>
       </c>
       <c r="AH13" s="4">
-        <f t="shared" si="27"/>
-        <v>343.17965616600009</v>
+        <f t="shared" si="21"/>
+        <v>307.48900689200008</v>
       </c>
       <c r="AI13" s="4">
-        <f t="shared" si="27"/>
-        <v>353.47504585098011</v>
+        <f t="shared" si="21"/>
+        <v>316.71367709876012</v>
       </c>
       <c r="AJ13" s="4">
-        <f t="shared" si="27"/>
-        <v>364.07929722650954</v>
+        <f t="shared" si="21"/>
+        <v>326.21508741172295</v>
       </c>
       <c r="AK13" s="4">
-        <f t="shared" si="27"/>
-        <v>375.00167614330485</v>
+        <f t="shared" si="21"/>
+        <v>336.00154003407465</v>
       </c>
       <c r="AL13" s="4">
-        <f t="shared" si="27"/>
-        <v>386.25172642760401</v>
+        <f t="shared" si="21"/>
+        <v>346.08158623509689</v>
       </c>
       <c r="AM13" s="4">
-        <f t="shared" si="27"/>
-        <v>397.83927822043216</v>
+        <f t="shared" si="21"/>
+        <v>356.46403382214982</v>
       </c>
       <c r="AN13" s="4">
-        <f t="shared" si="27"/>
-        <v>409.77445656704515</v>
+        <f t="shared" si="21"/>
+        <v>367.15795483681433</v>
       </c>
       <c r="AO13" s="4">
-        <f t="shared" si="27"/>
-        <v>422.06769026405652</v>
+        <f t="shared" si="21"/>
+        <v>378.17269348191877</v>
       </c>
     </row>
     <row r="14" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2518,140 +2496,140 @@
         <v>338</v>
       </c>
       <c r="G14" s="8">
-        <f t="shared" ref="G14:P14" si="28">G12-G13</f>
+        <f t="shared" ref="G14:P14" si="22">G12-G13</f>
         <v>416.49999999999955</v>
       </c>
       <c r="H14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>442.70000000000005</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>425.29999999999984</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>474.7000000000005</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>435.89999999999992</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>485.30000000000007</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>512.20000000000027</v>
       </c>
       <c r="N14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>583.50000000000034</v>
       </c>
       <c r="O14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>572.50000000000023</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>577.8000000000003</v>
       </c>
       <c r="Q14" s="8">
-        <f t="shared" ref="Q14:V14" si="29">Q12-Q13</f>
+        <f t="shared" ref="Q14:V14" si="23">Q12-Q13</f>
         <v>593.50000000000091</v>
       </c>
       <c r="R14" s="8">
-        <f t="shared" si="29"/>
-        <v>561.19999999999982</v>
+        <f t="shared" si="23"/>
+        <v>636</v>
       </c>
       <c r="S14" s="8">
-        <f t="shared" si="29"/>
-        <v>735.18619999999976</v>
+        <f t="shared" si="23"/>
+        <v>579.90000000000055</v>
       </c>
       <c r="T14" s="8">
-        <f t="shared" si="29"/>
-        <v>781.27600000000018</v>
+        <f t="shared" si="23"/>
+        <v>616.1999999999997</v>
       </c>
       <c r="U14" s="8">
-        <f t="shared" si="29"/>
-        <v>787.05881999999974</v>
+        <f t="shared" si="23"/>
+        <v>542.28652000000011</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" si="29"/>
-        <v>681.55960000000005</v>
+        <f t="shared" si="23"/>
+        <v>551.60739999999987</v>
       </c>
       <c r="X14" s="8">
-        <f t="shared" ref="X14:AD14" si="30">X12-X13</f>
+        <f t="shared" ref="X14:AD14" si="24">X12-X13</f>
         <v>1217.4999999999995</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>1912.4999999999989</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>1774.7000000000005</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>1488.0000000000011</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>1759.1999999999985</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>2016.9000000000003</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="24"/>
         <v>2379.7999999999961</v>
       </c>
       <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AO14" si="31">AE12-AE13</f>
-        <v>2985.0806199999997</v>
+        <f t="shared" ref="AE14:AO14" si="25">AE12-AE13</f>
+        <v>2289.9939199999994</v>
       </c>
       <c r="AF14" s="8">
-        <f t="shared" si="31"/>
-        <v>3271.090459800002</v>
+        <f t="shared" si="25"/>
+        <v>2580.0104039999997</v>
       </c>
       <c r="AG14" s="8">
-        <f t="shared" si="31"/>
-        <v>3544.8544479960001</v>
+        <f t="shared" si="25"/>
+        <v>3022.1103205999993</v>
       </c>
       <c r="AH14" s="8">
-        <f t="shared" si="31"/>
-        <v>3773.9445544759192</v>
+        <f t="shared" si="25"/>
+        <v>3240.9673078400006</v>
       </c>
       <c r="AI14" s="8">
-        <f t="shared" si="31"/>
-        <v>4004.3420568581773</v>
+        <f t="shared" si="25"/>
+        <v>3458.4398868182816</v>
       </c>
       <c r="AJ14" s="8">
-        <f t="shared" si="31"/>
-        <v>4130.8756518943956</v>
+        <f t="shared" si="25"/>
+        <v>3571.4521331288001</v>
       </c>
       <c r="AK14" s="8">
-        <f t="shared" si="31"/>
-        <v>4204.8074197381902</v>
+        <f t="shared" si="25"/>
+        <v>3686.4712629681653</v>
       </c>
       <c r="AL14" s="8">
-        <f t="shared" si="31"/>
-        <v>4200.4516127634188</v>
+        <f t="shared" si="25"/>
+        <v>3726.0510195307293</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" si="31"/>
-        <v>4188.1047682201533</v>
+        <f t="shared" si="25"/>
+        <v>3766.1080249769066</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" si="31"/>
-        <v>4166.7865333880854</v>
+        <f t="shared" si="25"/>
+        <v>3806.6494953350712</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" si="31"/>
-        <v>4135.6759505011496</v>
+        <f t="shared" si="25"/>
+        <v>3847.6827921000686</v>
       </c>
     </row>
     <row r="15" spans="2:150" x14ac:dyDescent="0.3">
@@ -2705,20 +2683,18 @@
         <v>-37</v>
       </c>
       <c r="S15" s="4">
-        <f>S14*0.18</f>
-        <v>132.33351599999995</v>
+        <v>54.8</v>
       </c>
       <c r="T15" s="4">
-        <f t="shared" ref="T15:V15" si="32">T14*0.18</f>
-        <v>140.62968000000004</v>
+        <v>79.5</v>
       </c>
       <c r="U15" s="4">
-        <f t="shared" si="32"/>
-        <v>141.67058759999995</v>
+        <f t="shared" ref="U15:V15" si="26">U14*0.15</f>
+        <v>81.342978000000016</v>
       </c>
       <c r="V15" s="4">
-        <f t="shared" si="32"/>
-        <v>122.680728</v>
+        <f t="shared" si="26"/>
+        <v>82.741109999999978</v>
       </c>
       <c r="X15" s="4">
         <v>307.2</v>
@@ -2744,47 +2720,47 @@
       </c>
       <c r="AE15" s="4">
         <f>SUM(S15:V15)</f>
-        <v>537.31451159999995</v>
+        <v>298.38408800000002</v>
       </c>
       <c r="AF15" s="4">
-        <f t="shared" ref="AF15:AO15" si="33">AF14*0.18</f>
-        <v>588.79628276400035</v>
+        <f t="shared" ref="AF15:AO15" si="27">AF14*0.18</f>
+        <v>464.40187271999991</v>
       </c>
       <c r="AG15" s="4">
-        <f t="shared" si="33"/>
-        <v>638.07380063927997</v>
+        <f t="shared" si="27"/>
+        <v>543.97985770799983</v>
       </c>
       <c r="AH15" s="4">
-        <f t="shared" si="33"/>
-        <v>679.31001980566543</v>
+        <f t="shared" si="27"/>
+        <v>583.37411541120002</v>
       </c>
       <c r="AI15" s="4">
-        <f t="shared" si="33"/>
-        <v>720.78157023447193</v>
+        <f t="shared" si="27"/>
+        <v>622.51917962729067</v>
       </c>
       <c r="AJ15" s="4">
-        <f t="shared" si="33"/>
-        <v>743.55761734099121</v>
+        <f t="shared" si="27"/>
+        <v>642.86138396318404</v>
       </c>
       <c r="AK15" s="4">
-        <f t="shared" si="33"/>
-        <v>756.86533555287417</v>
+        <f t="shared" si="27"/>
+        <v>663.56482733426969</v>
       </c>
       <c r="AL15" s="4">
-        <f t="shared" si="33"/>
-        <v>756.08129029741531</v>
+        <f t="shared" si="27"/>
+        <v>670.68918351553123</v>
       </c>
       <c r="AM15" s="4">
-        <f t="shared" si="33"/>
-        <v>753.85885827962761</v>
+        <f t="shared" si="27"/>
+        <v>677.89944449584311</v>
       </c>
       <c r="AN15" s="4">
-        <f t="shared" si="33"/>
-        <v>750.02157600985538</v>
+        <f t="shared" si="27"/>
+        <v>685.19690916031277</v>
       </c>
       <c r="AO15" s="4">
-        <f t="shared" si="33"/>
-        <v>744.42167109020693</v>
+        <f t="shared" si="27"/>
+        <v>692.58290257801229</v>
       </c>
     </row>
     <row r="16" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2800,576 +2776,576 @@
         <v>272</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" ref="G16:P16" si="34">G14-G15</f>
+        <f t="shared" ref="G16:P16" si="28">G14-G15</f>
         <v>349.89999999999952</v>
       </c>
       <c r="H16" s="8">
+        <f t="shared" si="28"/>
+        <v>366.90000000000003</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="28"/>
+        <v>380.29999999999984</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="28"/>
+        <v>407.60000000000048</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="28"/>
+        <v>369.69999999999993</v>
+      </c>
+      <c r="L16" s="8">
+        <f t="shared" si="28"/>
+        <v>427.40000000000009</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" si="28"/>
+        <v>410.90000000000026</v>
+      </c>
+      <c r="N16" s="8">
+        <f t="shared" si="28"/>
+        <v>445.5000000000004</v>
+      </c>
+      <c r="O16" s="8">
+        <f t="shared" si="28"/>
+        <v>482.70000000000022</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="28"/>
+        <v>503.70000000000027</v>
+      </c>
+      <c r="Q16" s="8">
+        <f t="shared" ref="Q16:R16" si="29">Q14-Q15</f>
+        <v>531.10000000000093</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" si="29"/>
+        <v>673</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" ref="S16:V16" si="30">S14-S15</f>
+        <v>525.10000000000059</v>
+      </c>
+      <c r="T16" s="8">
+        <f t="shared" si="30"/>
+        <v>536.6999999999997</v>
+      </c>
+      <c r="U16" s="8">
+        <f t="shared" si="30"/>
+        <v>460.94354200000009</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" si="30"/>
+        <v>468.86628999999988</v>
+      </c>
+      <c r="X16" s="8">
+        <f t="shared" ref="X16:AD16" si="31">X14-X15</f>
+        <v>910.2999999999995</v>
+      </c>
+      <c r="Y16" s="8">
+        <f t="shared" si="31"/>
+        <v>1366.9999999999989</v>
+      </c>
+      <c r="Z16" s="8">
+        <f t="shared" si="31"/>
+        <v>1292.3000000000006</v>
+      </c>
+      <c r="AA16" s="8">
+        <f t="shared" si="31"/>
+        <v>1166.3000000000011</v>
+      </c>
+      <c r="AB16" s="8">
+        <f t="shared" si="31"/>
+        <v>1504.6999999999985</v>
+      </c>
+      <c r="AC16" s="8">
+        <f t="shared" si="31"/>
+        <v>1653.5000000000005</v>
+      </c>
+      <c r="AD16" s="8">
+        <f t="shared" si="31"/>
+        <v>2190.4999999999959</v>
+      </c>
+      <c r="AE16" s="8">
+        <f t="shared" ref="AE16:AO16" si="32">AE14-AE15</f>
+        <v>1991.6098319999994</v>
+      </c>
+      <c r="AF16" s="8">
+        <f t="shared" si="32"/>
+        <v>2115.6085312799996</v>
+      </c>
+      <c r="AG16" s="8">
+        <f t="shared" si="32"/>
+        <v>2478.1304628919997</v>
+      </c>
+      <c r="AH16" s="8">
+        <f t="shared" si="32"/>
+        <v>2657.5931924288006</v>
+      </c>
+      <c r="AI16" s="8">
+        <f t="shared" si="32"/>
+        <v>2835.9207071909909</v>
+      </c>
+      <c r="AJ16" s="8">
+        <f t="shared" si="32"/>
+        <v>2928.5907491656162</v>
+      </c>
+      <c r="AK16" s="8">
+        <f t="shared" si="32"/>
+        <v>3022.9064356338959</v>
+      </c>
+      <c r="AL16" s="8">
+        <f t="shared" si="32"/>
+        <v>3055.3618360151982</v>
+      </c>
+      <c r="AM16" s="8">
+        <f t="shared" si="32"/>
+        <v>3088.2085804810636</v>
+      </c>
+      <c r="AN16" s="8">
+        <f t="shared" si="32"/>
+        <v>3121.4525861747584</v>
+      </c>
+      <c r="AO16" s="8">
+        <f t="shared" si="32"/>
+        <v>3155.0998895220564</v>
+      </c>
+      <c r="AP16" s="1">
+        <f t="shared" ref="AP16:BU16" si="33">AO16*(1+$AS$21)</f>
+        <v>3123.5488906268356</v>
+      </c>
+      <c r="AQ16" s="1">
+        <f t="shared" si="33"/>
+        <v>3092.3134017205671</v>
+      </c>
+      <c r="AR16" s="1">
+        <f t="shared" si="33"/>
+        <v>3061.3902677033616</v>
+      </c>
+      <c r="AS16" s="1">
+        <f t="shared" si="33"/>
+        <v>3030.7763650263278</v>
+      </c>
+      <c r="AT16" s="1">
+        <f t="shared" si="33"/>
+        <v>3000.4686013760643</v>
+      </c>
+      <c r="AU16" s="1">
+        <f t="shared" si="33"/>
+        <v>2970.4639153623034</v>
+      </c>
+      <c r="AV16" s="1">
+        <f t="shared" si="33"/>
+        <v>2940.7592762086801</v>
+      </c>
+      <c r="AW16" s="1">
+        <f t="shared" si="33"/>
+        <v>2911.3516834465931</v>
+      </c>
+      <c r="AX16" s="1">
+        <f t="shared" si="33"/>
+        <v>2882.2381666121273</v>
+      </c>
+      <c r="AY16" s="1">
+        <f t="shared" si="33"/>
+        <v>2853.4157849460062</v>
+      </c>
+      <c r="AZ16" s="1">
+        <f t="shared" si="33"/>
+        <v>2824.8816270965463</v>
+      </c>
+      <c r="BA16" s="1">
+        <f t="shared" si="33"/>
+        <v>2796.6328108255807</v>
+      </c>
+      <c r="BB16" s="1">
+        <f t="shared" si="33"/>
+        <v>2768.6664827173249</v>
+      </c>
+      <c r="BC16" s="1">
+        <f t="shared" si="33"/>
+        <v>2740.9798178901515</v>
+      </c>
+      <c r="BD16" s="1">
+        <f t="shared" si="33"/>
+        <v>2713.5700197112501</v>
+      </c>
+      <c r="BE16" s="1">
+        <f t="shared" si="33"/>
+        <v>2686.4343195141378</v>
+      </c>
+      <c r="BF16" s="1">
+        <f t="shared" si="33"/>
+        <v>2659.5699763189964</v>
+      </c>
+      <c r="BG16" s="1">
+        <f t="shared" si="33"/>
+        <v>2632.9742765558062</v>
+      </c>
+      <c r="BH16" s="1">
+        <f t="shared" si="33"/>
+        <v>2606.6445337902483</v>
+      </c>
+      <c r="BI16" s="1">
+        <f t="shared" si="33"/>
+        <v>2580.5780884523456</v>
+      </c>
+      <c r="BJ16" s="1">
+        <f t="shared" si="33"/>
+        <v>2554.7723075678223</v>
+      </c>
+      <c r="BK16" s="1">
+        <f t="shared" si="33"/>
+        <v>2529.224584492144</v>
+      </c>
+      <c r="BL16" s="1">
+        <f t="shared" si="33"/>
+        <v>2503.9323386472224</v>
+      </c>
+      <c r="BM16" s="1">
+        <f t="shared" si="33"/>
+        <v>2478.89301526075</v>
+      </c>
+      <c r="BN16" s="1">
+        <f t="shared" si="33"/>
+        <v>2454.1040851081425</v>
+      </c>
+      <c r="BO16" s="1">
+        <f t="shared" si="33"/>
+        <v>2429.5630442570609</v>
+      </c>
+      <c r="BP16" s="1">
+        <f t="shared" si="33"/>
+        <v>2405.2674138144903</v>
+      </c>
+      <c r="BQ16" s="1">
+        <f t="shared" si="33"/>
+        <v>2381.2147396763453</v>
+      </c>
+      <c r="BR16" s="1">
+        <f t="shared" si="33"/>
+        <v>2357.4025922795818</v>
+      </c>
+      <c r="BS16" s="1">
+        <f t="shared" si="33"/>
+        <v>2333.8285663567858</v>
+      </c>
+      <c r="BT16" s="1">
+        <f t="shared" si="33"/>
+        <v>2310.4902806932178</v>
+      </c>
+      <c r="BU16" s="1">
+        <f t="shared" si="33"/>
+        <v>2287.3853778862854</v>
+      </c>
+      <c r="BV16" s="1">
+        <f t="shared" ref="BV16:DA16" si="34">BU16*(1+$AS$21)</f>
+        <v>2264.5115241074227</v>
+      </c>
+      <c r="BW16" s="1">
         <f t="shared" si="34"/>
-        <v>366.90000000000003</v>
-      </c>
-      <c r="I16" s="8">
+        <v>2241.8664088663486</v>
+      </c>
+      <c r="BX16" s="1">
         <f t="shared" si="34"/>
-        <v>380.29999999999984</v>
-      </c>
-      <c r="J16" s="8">
+        <v>2219.4477447776849</v>
+      </c>
+      <c r="BY16" s="1">
         <f t="shared" si="34"/>
-        <v>407.60000000000048</v>
-      </c>
-      <c r="K16" s="8">
+        <v>2197.2532673299079</v>
+      </c>
+      <c r="BZ16" s="1">
         <f t="shared" si="34"/>
-        <v>369.69999999999993</v>
-      </c>
-      <c r="L16" s="8">
+        <v>2175.2807346566087</v>
+      </c>
+      <c r="CA16" s="1">
         <f t="shared" si="34"/>
-        <v>427.40000000000009</v>
-      </c>
-      <c r="M16" s="8">
+        <v>2153.5279273100427</v>
+      </c>
+      <c r="CB16" s="1">
         <f t="shared" si="34"/>
-        <v>410.90000000000026</v>
-      </c>
-      <c r="N16" s="8">
+        <v>2131.9926480369422</v>
+      </c>
+      <c r="CC16" s="1">
         <f t="shared" si="34"/>
-        <v>445.5000000000004</v>
-      </c>
-      <c r="O16" s="8">
+        <v>2110.6727215565729</v>
+      </c>
+      <c r="CD16" s="1">
         <f t="shared" si="34"/>
-        <v>482.70000000000022</v>
-      </c>
-      <c r="P16" s="8">
+        <v>2089.5659943410074</v>
+      </c>
+      <c r="CE16" s="1">
         <f t="shared" si="34"/>
-        <v>503.70000000000027</v>
-      </c>
-      <c r="Q16" s="8">
-        <f t="shared" ref="Q16:R16" si="35">Q14-Q15</f>
-        <v>531.10000000000093</v>
-      </c>
-      <c r="R16" s="8">
+        <v>2068.6703343975973</v>
+      </c>
+      <c r="CF16" s="1">
+        <f t="shared" si="34"/>
+        <v>2047.9836310536214</v>
+      </c>
+      <c r="CG16" s="1">
+        <f t="shared" si="34"/>
+        <v>2027.5037947430851</v>
+      </c>
+      <c r="CH16" s="1">
+        <f t="shared" si="34"/>
+        <v>2007.2287567956541</v>
+      </c>
+      <c r="CI16" s="1">
+        <f t="shared" si="34"/>
+        <v>1987.1564692276975</v>
+      </c>
+      <c r="CJ16" s="1">
+        <f t="shared" si="34"/>
+        <v>1967.2849045354205</v>
+      </c>
+      <c r="CK16" s="1">
+        <f t="shared" si="34"/>
+        <v>1947.6120554900663</v>
+      </c>
+      <c r="CL16" s="1">
+        <f t="shared" si="34"/>
+        <v>1928.1359349351656</v>
+      </c>
+      <c r="CM16" s="1">
+        <f t="shared" si="34"/>
+        <v>1908.8545755858138</v>
+      </c>
+      <c r="CN16" s="1">
+        <f t="shared" si="34"/>
+        <v>1889.7660298299556</v>
+      </c>
+      <c r="CO16" s="1">
+        <f t="shared" si="34"/>
+        <v>1870.8683695316561</v>
+      </c>
+      <c r="CP16" s="1">
+        <f t="shared" si="34"/>
+        <v>1852.1596858363396</v>
+      </c>
+      <c r="CQ16" s="1">
+        <f t="shared" si="34"/>
+        <v>1833.6380889779762</v>
+      </c>
+      <c r="CR16" s="1">
+        <f t="shared" si="34"/>
+        <v>1815.3017080881964</v>
+      </c>
+      <c r="CS16" s="1">
+        <f t="shared" si="34"/>
+        <v>1797.1486910073145</v>
+      </c>
+      <c r="CT16" s="1">
+        <f t="shared" si="34"/>
+        <v>1779.1772040972414</v>
+      </c>
+      <c r="CU16" s="1">
+        <f t="shared" si="34"/>
+        <v>1761.3854320562691</v>
+      </c>
+      <c r="CV16" s="1">
+        <f t="shared" si="34"/>
+        <v>1743.7715777357064</v>
+      </c>
+      <c r="CW16" s="1">
+        <f t="shared" si="34"/>
+        <v>1726.3338619583494</v>
+      </c>
+      <c r="CX16" s="1">
+        <f t="shared" si="34"/>
+        <v>1709.070523338766</v>
+      </c>
+      <c r="CY16" s="1">
+        <f t="shared" si="34"/>
+        <v>1691.9798181053782</v>
+      </c>
+      <c r="CZ16" s="1">
+        <f t="shared" si="34"/>
+        <v>1675.0600199243245</v>
+      </c>
+      <c r="DA16" s="1">
+        <f t="shared" si="34"/>
+        <v>1658.3094197250812</v>
+      </c>
+      <c r="DB16" s="1">
+        <f t="shared" ref="DB16:EG16" si="35">DA16*(1+$AS$21)</f>
+        <v>1641.7263255278303</v>
+      </c>
+      <c r="DC16" s="1">
         <f t="shared" si="35"/>
-        <v>598.19999999999982</v>
-      </c>
-      <c r="S16" s="8">
-        <f t="shared" ref="S16:V16" si="36">S14-S15</f>
-        <v>602.85268399999984</v>
-      </c>
-      <c r="T16" s="8">
+        <v>1625.309062272552</v>
+      </c>
+      <c r="DD16" s="1">
+        <f t="shared" si="35"/>
+        <v>1609.0559716498265</v>
+      </c>
+      <c r="DE16" s="1">
+        <f t="shared" si="35"/>
+        <v>1592.9654119333281</v>
+      </c>
+      <c r="DF16" s="1">
+        <f t="shared" si="35"/>
+        <v>1577.0357578139949</v>
+      </c>
+      <c r="DG16" s="1">
+        <f t="shared" si="35"/>
+        <v>1561.2654002358549</v>
+      </c>
+      <c r="DH16" s="1">
+        <f t="shared" si="35"/>
+        <v>1545.6527462334964</v>
+      </c>
+      <c r="DI16" s="1">
+        <f t="shared" si="35"/>
+        <v>1530.1962187711613</v>
+      </c>
+      <c r="DJ16" s="1">
+        <f t="shared" si="35"/>
+        <v>1514.8942565834498</v>
+      </c>
+      <c r="DK16" s="1">
+        <f t="shared" si="35"/>
+        <v>1499.7453140176153</v>
+      </c>
+      <c r="DL16" s="1">
+        <f t="shared" si="35"/>
+        <v>1484.7478608774391</v>
+      </c>
+      <c r="DM16" s="1">
+        <f t="shared" si="35"/>
+        <v>1469.9003822686645</v>
+      </c>
+      <c r="DN16" s="1">
+        <f t="shared" si="35"/>
+        <v>1455.201378445978</v>
+      </c>
+      <c r="DO16" s="1">
+        <f t="shared" si="35"/>
+        <v>1440.6493646615181</v>
+      </c>
+      <c r="DP16" s="1">
+        <f t="shared" si="35"/>
+        <v>1426.2428710149029</v>
+      </c>
+      <c r="DQ16" s="1">
+        <f t="shared" si="35"/>
+        <v>1411.9804423047538</v>
+      </c>
+      <c r="DR16" s="1">
+        <f t="shared" si="35"/>
+        <v>1397.8606378817062</v>
+      </c>
+      <c r="DS16" s="1">
+        <f t="shared" si="35"/>
+        <v>1383.882031502889</v>
+      </c>
+      <c r="DT16" s="1">
+        <f t="shared" si="35"/>
+        <v>1370.0432111878602</v>
+      </c>
+      <c r="DU16" s="1">
+        <f t="shared" si="35"/>
+        <v>1356.3427790759815</v>
+      </c>
+      <c r="DV16" s="1">
+        <f t="shared" si="35"/>
+        <v>1342.7793512852218</v>
+      </c>
+      <c r="DW16" s="1">
+        <f t="shared" si="35"/>
+        <v>1329.3515577723695</v>
+      </c>
+      <c r="DX16" s="1">
+        <f t="shared" si="35"/>
+        <v>1316.0580421946459</v>
+      </c>
+      <c r="DY16" s="1">
+        <f t="shared" si="35"/>
+        <v>1302.8974617726994</v>
+      </c>
+      <c r="DZ16" s="1">
+        <f t="shared" si="35"/>
+        <v>1289.8684871549724</v>
+      </c>
+      <c r="EA16" s="1">
+        <f t="shared" si="35"/>
+        <v>1276.9698022834227</v>
+      </c>
+      <c r="EB16" s="1">
+        <f t="shared" si="35"/>
+        <v>1264.2001042605884</v>
+      </c>
+      <c r="EC16" s="1">
+        <f t="shared" si="35"/>
+        <v>1251.5581032179825</v>
+      </c>
+      <c r="ED16" s="1">
+        <f t="shared" si="35"/>
+        <v>1239.0425221858027</v>
+      </c>
+      <c r="EE16" s="1">
+        <f t="shared" si="35"/>
+        <v>1226.6520969639446</v>
+      </c>
+      <c r="EF16" s="1">
+        <f t="shared" si="35"/>
+        <v>1214.3855759943051</v>
+      </c>
+      <c r="EG16" s="1">
+        <f t="shared" si="35"/>
+        <v>1202.241720234362</v>
+      </c>
+      <c r="EH16" s="1">
+        <f t="shared" ref="EH16:ET16" si="36">EG16*(1+$AS$21)</f>
+        <v>1190.2193030320184</v>
+      </c>
+      <c r="EI16" s="1">
         <f t="shared" si="36"/>
-        <v>640.64632000000017</v>
-      </c>
-      <c r="U16" s="8">
+        <v>1178.3171100016982</v>
+      </c>
+      <c r="EJ16" s="1">
         <f t="shared" si="36"/>
-        <v>645.38823239999977</v>
-      </c>
-      <c r="V16" s="8">
+        <v>1166.5339389016813</v>
+      </c>
+      <c r="EK16" s="1">
         <f t="shared" si="36"/>
-        <v>558.878872</v>
-      </c>
-      <c r="X16" s="8">
-        <f t="shared" ref="X16:AD16" si="37">X14-X15</f>
-        <v>910.2999999999995</v>
-      </c>
-      <c r="Y16" s="8">
-        <f t="shared" si="37"/>
-        <v>1366.9999999999989</v>
-      </c>
-      <c r="Z16" s="8">
-        <f t="shared" si="37"/>
-        <v>1292.3000000000006</v>
-      </c>
-      <c r="AA16" s="8">
-        <f t="shared" si="37"/>
-        <v>1166.3000000000011</v>
-      </c>
-      <c r="AB16" s="8">
-        <f t="shared" si="37"/>
-        <v>1504.6999999999985</v>
-      </c>
-      <c r="AC16" s="8">
-        <f t="shared" si="37"/>
-        <v>1653.5000000000005</v>
-      </c>
-      <c r="AD16" s="8">
-        <f t="shared" si="37"/>
-        <v>2190.4999999999959</v>
-      </c>
-      <c r="AE16" s="8">
-        <f t="shared" ref="AE16:AO16" si="38">AE14-AE15</f>
-        <v>2447.7661083999997</v>
-      </c>
-      <c r="AF16" s="8">
-        <f t="shared" si="38"/>
-        <v>2682.2941770360017</v>
-      </c>
-      <c r="AG16" s="8">
-        <f t="shared" si="38"/>
-        <v>2906.7806473567202</v>
-      </c>
-      <c r="AH16" s="8">
-        <f t="shared" si="38"/>
-        <v>3094.6345346702537</v>
-      </c>
-      <c r="AI16" s="8">
-        <f t="shared" si="38"/>
-        <v>3283.5604866237054</v>
-      </c>
-      <c r="AJ16" s="8">
-        <f t="shared" si="38"/>
-        <v>3387.3180345534042</v>
-      </c>
-      <c r="AK16" s="8">
-        <f t="shared" si="38"/>
-        <v>3447.9420841853162</v>
-      </c>
-      <c r="AL16" s="8">
-        <f t="shared" si="38"/>
-        <v>3444.3703224660035</v>
-      </c>
-      <c r="AM16" s="8">
-        <f t="shared" si="38"/>
-        <v>3434.245909940526</v>
-      </c>
-      <c r="AN16" s="8">
-        <f t="shared" si="38"/>
-        <v>3416.7649573782301</v>
-      </c>
-      <c r="AO16" s="8">
-        <f t="shared" si="38"/>
-        <v>3391.2542794109427</v>
-      </c>
-      <c r="AP16" s="1">
-        <f t="shared" ref="AP16:BU16" si="39">AO16*(1+$AS$21)</f>
-        <v>3357.3417366168333</v>
-      </c>
-      <c r="AQ16" s="1">
-        <f t="shared" si="39"/>
-        <v>3323.7683192506647</v>
-      </c>
-      <c r="AR16" s="1">
-        <f t="shared" si="39"/>
-        <v>3290.5306360581581</v>
-      </c>
-      <c r="AS16" s="1">
-        <f t="shared" si="39"/>
-        <v>3257.6253296975765</v>
-      </c>
-      <c r="AT16" s="1">
-        <f t="shared" si="39"/>
-        <v>3225.0490764006008</v>
-      </c>
-      <c r="AU16" s="1">
-        <f t="shared" si="39"/>
-        <v>3192.7985856365949</v>
-      </c>
-      <c r="AV16" s="1">
-        <f t="shared" si="39"/>
-        <v>3160.870599780229</v>
-      </c>
-      <c r="AW16" s="1">
-        <f t="shared" si="39"/>
-        <v>3129.2618937824268</v>
-      </c>
-      <c r="AX16" s="1">
-        <f t="shared" si="39"/>
-        <v>3097.9692748446023</v>
-      </c>
-      <c r="AY16" s="1">
-        <f t="shared" si="39"/>
-        <v>3066.989582096156</v>
-      </c>
-      <c r="AZ16" s="1">
-        <f t="shared" si="39"/>
-        <v>3036.3196862751943</v>
-      </c>
-      <c r="BA16" s="1">
-        <f t="shared" si="39"/>
-        <v>3005.9564894124424</v>
-      </c>
-      <c r="BB16" s="1">
-        <f t="shared" si="39"/>
-        <v>2975.896924518318</v>
-      </c>
-      <c r="BC16" s="1">
-        <f t="shared" si="39"/>
-        <v>2946.1379552731346</v>
-      </c>
-      <c r="BD16" s="1">
-        <f t="shared" si="39"/>
-        <v>2916.6765757204034</v>
-      </c>
-      <c r="BE16" s="1">
-        <f t="shared" si="39"/>
-        <v>2887.5098099631996</v>
-      </c>
-      <c r="BF16" s="1">
-        <f t="shared" si="39"/>
-        <v>2858.6347118635676</v>
-      </c>
-      <c r="BG16" s="1">
-        <f t="shared" si="39"/>
-        <v>2830.0483647449319</v>
-      </c>
-      <c r="BH16" s="1">
-        <f t="shared" si="39"/>
-        <v>2801.7478810974826</v>
-      </c>
-      <c r="BI16" s="1">
-        <f t="shared" si="39"/>
-        <v>2773.7304022865078</v>
-      </c>
-      <c r="BJ16" s="1">
-        <f t="shared" si="39"/>
-        <v>2745.9930982636429</v>
-      </c>
-      <c r="BK16" s="1">
-        <f t="shared" si="39"/>
-        <v>2718.5331672810066</v>
-      </c>
-      <c r="BL16" s="1">
-        <f t="shared" si="39"/>
-        <v>2691.3478356081964</v>
-      </c>
-      <c r="BM16" s="1">
-        <f t="shared" si="39"/>
-        <v>2664.4343572521143</v>
-      </c>
-      <c r="BN16" s="1">
-        <f t="shared" si="39"/>
-        <v>2637.7900136795929</v>
-      </c>
-      <c r="BO16" s="1">
-        <f t="shared" si="39"/>
-        <v>2611.4121135427968</v>
-      </c>
-      <c r="BP16" s="1">
-        <f t="shared" si="39"/>
-        <v>2585.2979924073688</v>
-      </c>
-      <c r="BQ16" s="1">
-        <f t="shared" si="39"/>
-        <v>2559.4450124832952</v>
-      </c>
-      <c r="BR16" s="1">
-        <f t="shared" si="39"/>
-        <v>2533.8505623584624</v>
-      </c>
-      <c r="BS16" s="1">
-        <f t="shared" si="39"/>
-        <v>2508.5120567348777</v>
-      </c>
-      <c r="BT16" s="1">
-        <f t="shared" si="39"/>
-        <v>2483.4269361675288</v>
-      </c>
-      <c r="BU16" s="1">
-        <f t="shared" si="39"/>
-        <v>2458.5926668058532</v>
-      </c>
-      <c r="BV16" s="1">
-        <f t="shared" ref="BV16:DA16" si="40">BU16*(1+$AS$21)</f>
-        <v>2434.0067401377946</v>
-      </c>
-      <c r="BW16" s="1">
-        <f t="shared" si="40"/>
-        <v>2409.6666727364168</v>
-      </c>
-      <c r="BX16" s="1">
-        <f t="shared" si="40"/>
-        <v>2385.5700060090526</v>
-      </c>
-      <c r="BY16" s="1">
-        <f t="shared" si="40"/>
-        <v>2361.7143059489622</v>
-      </c>
-      <c r="BZ16" s="1">
-        <f t="shared" si="40"/>
-        <v>2338.0971628894727</v>
-      </c>
-      <c r="CA16" s="1">
-        <f t="shared" si="40"/>
-        <v>2314.7161912605779</v>
-      </c>
-      <c r="CB16" s="1">
-        <f t="shared" si="40"/>
-        <v>2291.569029347972</v>
-      </c>
-      <c r="CC16" s="1">
-        <f t="shared" si="40"/>
-        <v>2268.6533390544923</v>
-      </c>
-      <c r="CD16" s="1">
-        <f t="shared" si="40"/>
-        <v>2245.9668056639475</v>
-      </c>
-      <c r="CE16" s="1">
-        <f t="shared" si="40"/>
-        <v>2223.5071376073079</v>
-      </c>
-      <c r="CF16" s="1">
-        <f t="shared" si="40"/>
-        <v>2201.2720662312349</v>
-      </c>
-      <c r="CG16" s="1">
-        <f t="shared" si="40"/>
-        <v>2179.2593455689225</v>
-      </c>
-      <c r="CH16" s="1">
-        <f t="shared" si="40"/>
-        <v>2157.4667521132333</v>
-      </c>
-      <c r="CI16" s="1">
-        <f t="shared" si="40"/>
-        <v>2135.8920845921011</v>
-      </c>
-      <c r="CJ16" s="1">
-        <f t="shared" si="40"/>
-        <v>2114.53316374618</v>
-      </c>
-      <c r="CK16" s="1">
-        <f t="shared" si="40"/>
-        <v>2093.3878321087182</v>
-      </c>
-      <c r="CL16" s="1">
-        <f t="shared" si="40"/>
-        <v>2072.4539537876308</v>
-      </c>
-      <c r="CM16" s="1">
-        <f t="shared" si="40"/>
-        <v>2051.7294142497544</v>
-      </c>
-      <c r="CN16" s="1">
-        <f t="shared" si="40"/>
-        <v>2031.2121201072569</v>
-      </c>
-      <c r="CO16" s="1">
-        <f t="shared" si="40"/>
-        <v>2010.8999989061842</v>
-      </c>
-      <c r="CP16" s="1">
-        <f t="shared" si="40"/>
-        <v>1990.7909989171224</v>
-      </c>
-      <c r="CQ16" s="1">
-        <f t="shared" si="40"/>
-        <v>1970.8830889279511</v>
-      </c>
-      <c r="CR16" s="1">
-        <f t="shared" si="40"/>
-        <v>1951.1742580386715</v>
-      </c>
-      <c r="CS16" s="1">
-        <f t="shared" si="40"/>
-        <v>1931.6625154582848</v>
-      </c>
-      <c r="CT16" s="1">
-        <f t="shared" si="40"/>
-        <v>1912.3458903037019</v>
-      </c>
-      <c r="CU16" s="1">
-        <f t="shared" si="40"/>
-        <v>1893.2224314006648</v>
-      </c>
-      <c r="CV16" s="1">
-        <f t="shared" si="40"/>
-        <v>1874.2902070866583</v>
-      </c>
-      <c r="CW16" s="1">
-        <f t="shared" si="40"/>
-        <v>1855.5473050157916</v>
-      </c>
-      <c r="CX16" s="1">
-        <f t="shared" si="40"/>
-        <v>1836.9918319656338</v>
-      </c>
-      <c r="CY16" s="1">
-        <f t="shared" si="40"/>
-        <v>1818.6219136459774</v>
-      </c>
-      <c r="CZ16" s="1">
-        <f t="shared" si="40"/>
-        <v>1800.4356945095176</v>
-      </c>
-      <c r="DA16" s="1">
-        <f t="shared" si="40"/>
-        <v>1782.4313375644224</v>
-      </c>
-      <c r="DB16" s="1">
-        <f t="shared" ref="DB16:EG16" si="41">DA16*(1+$AS$21)</f>
-        <v>1764.607024188778</v>
-      </c>
-      <c r="DC16" s="1">
-        <f t="shared" si="41"/>
-        <v>1746.9609539468902</v>
-      </c>
-      <c r="DD16" s="1">
-        <f t="shared" si="41"/>
-        <v>1729.4913444074214</v>
-      </c>
-      <c r="DE16" s="1">
-        <f t="shared" si="41"/>
-        <v>1712.1964309633472</v>
-      </c>
-      <c r="DF16" s="1">
-        <f t="shared" si="41"/>
-        <v>1695.0744666537137</v>
-      </c>
-      <c r="DG16" s="1">
-        <f t="shared" si="41"/>
-        <v>1678.1237219871766</v>
-      </c>
-      <c r="DH16" s="1">
-        <f t="shared" si="41"/>
-        <v>1661.3424847673048</v>
-      </c>
-      <c r="DI16" s="1">
-        <f t="shared" si="41"/>
-        <v>1644.7290599196317</v>
-      </c>
-      <c r="DJ16" s="1">
-        <f t="shared" si="41"/>
-        <v>1628.2817693204354</v>
-      </c>
-      <c r="DK16" s="1">
-        <f t="shared" si="41"/>
-        <v>1611.998951627231</v>
-      </c>
-      <c r="DL16" s="1">
-        <f t="shared" si="41"/>
-        <v>1595.8789621109586</v>
-      </c>
-      <c r="DM16" s="1">
-        <f t="shared" si="41"/>
-        <v>1579.9201724898489</v>
-      </c>
-      <c r="DN16" s="1">
-        <f t="shared" si="41"/>
-        <v>1564.1209707649505</v>
-      </c>
-      <c r="DO16" s="1">
-        <f t="shared" si="41"/>
-        <v>1548.4797610573009</v>
-      </c>
-      <c r="DP16" s="1">
-        <f t="shared" si="41"/>
-        <v>1532.994963446728</v>
-      </c>
-      <c r="DQ16" s="1">
-        <f t="shared" si="41"/>
-        <v>1517.6650138122607</v>
-      </c>
-      <c r="DR16" s="1">
-        <f t="shared" si="41"/>
-        <v>1502.4883636741381</v>
-      </c>
-      <c r="DS16" s="1">
-        <f t="shared" si="41"/>
-        <v>1487.4634800373967</v>
-      </c>
-      <c r="DT16" s="1">
-        <f t="shared" si="41"/>
-        <v>1472.5888452370227</v>
-      </c>
-      <c r="DU16" s="1">
-        <f t="shared" si="41"/>
-        <v>1457.8629567846524</v>
-      </c>
-      <c r="DV16" s="1">
-        <f t="shared" si="41"/>
-        <v>1443.2843272168059</v>
-      </c>
-      <c r="DW16" s="1">
-        <f t="shared" si="41"/>
-        <v>1428.8514839446377</v>
-      </c>
-      <c r="DX16" s="1">
-        <f t="shared" si="41"/>
-        <v>1414.5629691051913</v>
-      </c>
-      <c r="DY16" s="1">
-        <f t="shared" si="41"/>
-        <v>1400.4173394141394</v>
-      </c>
-      <c r="DZ16" s="1">
-        <f t="shared" si="41"/>
-        <v>1386.413166019998</v>
-      </c>
-      <c r="EA16" s="1">
-        <f t="shared" si="41"/>
-        <v>1372.549034359798</v>
-      </c>
-      <c r="EB16" s="1">
-        <f t="shared" si="41"/>
-        <v>1358.8235440162</v>
-      </c>
-      <c r="EC16" s="1">
-        <f t="shared" si="41"/>
-        <v>1345.2353085760381</v>
-      </c>
-      <c r="ED16" s="1">
-        <f t="shared" si="41"/>
-        <v>1331.7829554902776</v>
-      </c>
-      <c r="EE16" s="1">
-        <f t="shared" si="41"/>
-        <v>1318.4651259353748</v>
-      </c>
-      <c r="EF16" s="1">
-        <f t="shared" si="41"/>
-        <v>1305.280474676021</v>
-      </c>
-      <c r="EG16" s="1">
-        <f t="shared" si="41"/>
-        <v>1292.2276699292606</v>
-      </c>
-      <c r="EH16" s="1">
-        <f t="shared" ref="EH16:ET16" si="42">EG16*(1+$AS$21)</f>
-        <v>1279.3053932299681</v>
-      </c>
-      <c r="EI16" s="1">
-        <f t="shared" si="42"/>
-        <v>1266.5123392976684</v>
-      </c>
-      <c r="EJ16" s="1">
-        <f t="shared" si="42"/>
-        <v>1253.8472159046917</v>
-      </c>
-      <c r="EK16" s="1">
-        <f t="shared" si="42"/>
-        <v>1241.3087437456447</v>
+        <v>1154.8685995126643</v>
       </c>
       <c r="EL16" s="1">
-        <f t="shared" si="42"/>
-        <v>1228.8956563081883</v>
+        <f t="shared" si="36"/>
+        <v>1143.3199135175378</v>
       </c>
       <c r="EM16" s="1">
-        <f t="shared" si="42"/>
-        <v>1216.6066997451064</v>
+        <f t="shared" si="36"/>
+        <v>1131.8867143823625</v>
       </c>
       <c r="EN16" s="1">
-        <f t="shared" si="42"/>
-        <v>1204.4406327476554</v>
+        <f t="shared" si="36"/>
+        <v>1120.5678472385389</v>
       </c>
       <c r="EO16" s="1">
-        <f t="shared" si="42"/>
-        <v>1192.3962264201789</v>
+        <f t="shared" si="36"/>
+        <v>1109.3621687661534</v>
       </c>
       <c r="EP16" s="1">
-        <f t="shared" si="42"/>
-        <v>1180.4722641559772</v>
+        <f t="shared" si="36"/>
+        <v>1098.2685470784918</v>
       </c>
       <c r="EQ16" s="1">
-        <f t="shared" si="42"/>
-        <v>1168.6675415144175</v>
+        <f t="shared" si="36"/>
+        <v>1087.2858616077069</v>
       </c>
       <c r="ER16" s="1">
-        <f t="shared" si="42"/>
-        <v>1156.9808660992733</v>
+        <f t="shared" si="36"/>
+        <v>1076.4130029916298</v>
       </c>
       <c r="ES16" s="1">
-        <f t="shared" si="42"/>
-        <v>1145.4110574382805</v>
+        <f t="shared" si="36"/>
+        <v>1065.6488729617136</v>
       </c>
       <c r="ET16" s="1">
-        <f t="shared" si="42"/>
-        <v>1133.9569468638977</v>
+        <f t="shared" si="36"/>
+        <v>1054.9923842320964</v>
       </c>
     </row>
     <row r="17" spans="2:45" x14ac:dyDescent="0.3">
@@ -3421,20 +3397,20 @@
         <v>316.10000000000002</v>
       </c>
       <c r="S17" s="4">
-        <f t="shared" ref="S17:V17" si="43">316.1</f>
-        <v>316.10000000000002</v>
+        <f>303.6</f>
+        <v>303.60000000000002</v>
       </c>
       <c r="T17" s="4">
-        <f t="shared" si="43"/>
-        <v>316.10000000000002</v>
+        <f>297.7</f>
+        <v>297.7</v>
       </c>
       <c r="U17" s="4">
-        <f t="shared" si="43"/>
-        <v>316.10000000000002</v>
+        <f>297.7</f>
+        <v>297.7</v>
       </c>
       <c r="V17" s="4">
-        <f t="shared" si="43"/>
-        <v>316.10000000000002</v>
+        <f>297.7</f>
+        <v>297.7</v>
       </c>
       <c r="X17" s="4">
         <v>319.10000000000002</v>
@@ -3455,52 +3431,52 @@
         <v>319.10000000000002</v>
       </c>
       <c r="AD17" s="4">
-        <f t="shared" ref="AD17:AO17" si="44">316.1</f>
+        <f t="shared" ref="AD17" si="37">316.1</f>
         <v>316.10000000000002</v>
       </c>
       <c r="AE17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" ref="AE17:AO17" si="38">297.7</f>
+        <v>297.7</v>
       </c>
       <c r="AF17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AG17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AH17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AI17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AJ17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AK17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AL17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AM17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AN17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
       <c r="AO17" s="4">
-        <f t="shared" si="44"/>
-        <v>316.10000000000002</v>
+        <f t="shared" si="38"/>
+        <v>297.7</v>
       </c>
     </row>
     <row r="18" spans="2:45" x14ac:dyDescent="0.3">
@@ -3516,140 +3492,140 @@
         <v>0.85239736759636475</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" ref="G18:P18" si="45">G16/G17</f>
+        <f t="shared" ref="G18:P18" si="39">G16/G17</f>
         <v>1.0965214666248808</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.1497963020996553</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.1917894077091815</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.2773425258539657</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.1585709808837352</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.3393920401128174</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.2876841115637738</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.3961140708241941</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.5126919460984023</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>1.5785020369790042</v>
       </c>
       <c r="Q18" s="7">
-        <f t="shared" ref="Q18:R18" si="46">Q16/Q17</f>
+        <f t="shared" ref="Q18:R18" si="40">Q16/Q17</f>
         <v>1.6722292191435797</v>
       </c>
       <c r="R18" s="7">
-        <f t="shared" si="46"/>
-        <v>1.8924391015501416</v>
+        <f t="shared" si="40"/>
+        <v>2.1290730781398288</v>
       </c>
       <c r="S18" s="7">
-        <f t="shared" ref="S18:V18" si="47">S16/S17</f>
-        <v>1.907158127174944</v>
+        <f t="shared" ref="S18:V18" si="41">S16/S17</f>
+        <v>1.7295783926218726</v>
       </c>
       <c r="T18" s="7">
-        <f t="shared" si="47"/>
-        <v>2.0267204049351477</v>
+        <f t="shared" si="41"/>
+        <v>1.8028216325159547</v>
       </c>
       <c r="U18" s="7">
-        <f t="shared" si="47"/>
-        <v>2.0417217095855733</v>
+        <f t="shared" si="41"/>
+        <v>1.5483491501511593</v>
       </c>
       <c r="V18" s="7">
-        <f t="shared" si="47"/>
-        <v>1.7680445175577348</v>
+        <f t="shared" si="41"/>
+        <v>1.5749623446422569</v>
       </c>
       <c r="X18" s="7">
-        <f t="shared" ref="X18:AD18" si="48">X16/X17</f>
+        <f t="shared" ref="X18:AD18" si="42">X16/X17</f>
         <v>2.8527107489815089</v>
       </c>
       <c r="Y18" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>4.2839235349420202</v>
       </c>
       <c r="Z18" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>4.0498276402381714</v>
       </c>
       <c r="AA18" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>3.654967094954563</v>
       </c>
       <c r="AB18" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>4.7154497022876791</v>
       </c>
       <c r="AC18" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>5.1817612033845197</v>
       </c>
       <c r="AD18" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>6.9297690604239026</v>
       </c>
       <c r="AE18" s="7">
-        <f t="shared" ref="AE18:AO18" si="49">AE16/AE17</f>
-        <v>7.7436447592533995</v>
+        <f t="shared" ref="AE18:AO18" si="43">AE16/AE17</f>
+        <v>6.6899893584145094</v>
       </c>
       <c r="AF18" s="7">
-        <f t="shared" si="49"/>
-        <v>8.4855873996709956</v>
+        <f t="shared" si="43"/>
+        <v>7.1065116939200523</v>
       </c>
       <c r="AG18" s="7">
-        <f t="shared" si="49"/>
-        <v>9.1957628831278715</v>
+        <f t="shared" si="43"/>
+        <v>8.3242541581860934</v>
       </c>
       <c r="AH18" s="7">
-        <f t="shared" si="49"/>
-        <v>9.7900491447967521</v>
+        <f t="shared" si="43"/>
+        <v>8.9270849594518005</v>
       </c>
       <c r="AI18" s="7">
-        <f t="shared" si="49"/>
-        <v>10.387726942814632</v>
+        <f t="shared" si="43"/>
+        <v>9.5261024762881803</v>
       </c>
       <c r="AJ18" s="7">
-        <f t="shared" si="49"/>
-        <v>10.715969739175589</v>
+        <f t="shared" si="43"/>
+        <v>9.837389147348393</v>
       </c>
       <c r="AK18" s="7">
-        <f t="shared" si="49"/>
-        <v>10.907757305236684</v>
+        <f t="shared" si="43"/>
+        <v>10.154203680328841</v>
       </c>
       <c r="AL18" s="7">
-        <f t="shared" si="49"/>
-        <v>10.896457837602036</v>
+        <f t="shared" si="43"/>
+        <v>10.263224172036272</v>
       </c>
       <c r="AM18" s="7">
-        <f t="shared" si="49"/>
-        <v>10.864428693263289</v>
+        <f t="shared" si="43"/>
+        <v>10.373559222307906</v>
       </c>
       <c r="AN18" s="7">
-        <f t="shared" si="49"/>
-        <v>10.809126723752705</v>
+        <f t="shared" si="43"/>
+        <v>10.485228707338793</v>
       </c>
       <c r="AO18" s="7">
-        <f t="shared" si="49"/>
-        <v>10.728422269569574</v>
+        <f t="shared" si="43"/>
+        <v>10.598252904004221</v>
       </c>
     </row>
     <row r="20" spans="2:45" x14ac:dyDescent="0.3">
@@ -3657,29 +3633,29 @@
         <v>41</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" ref="G20:N23" si="50">G3/C3-1</f>
+        <f t="shared" ref="G20:N23" si="44">G3/C3-1</f>
         <v>0.48346570397111899</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>0.4570764162521801</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>4.6919108342256433E-2</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>-3.976592631998932E-2</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>-9.9472099821124038E-3</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>5.9418402777778212E-2</v>
       </c>
       <c r="O20" s="9">
@@ -3687,32 +3663,32 @@
         <v>0.10153417015341715</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" ref="P20:P23" si="51">P3/L3-1</f>
+        <f t="shared" ref="P20:P23" si="45">P3/L3-1</f>
         <v>6.7405355493998176E-2</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20:Q23" si="52">Q3/M3-1</f>
+        <f t="shared" ref="Q20:Q23" si="46">Q3/M3-1</f>
         <v>-4.142246507733649E-3</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" ref="R20:R23" si="53">R3/N3-1</f>
+        <f t="shared" ref="R20:R23" si="47">R3/N3-1</f>
         <v>-8.1486337006841936E-2</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20:S23" si="54">S3/O3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="S20:S23" si="48">S3/O3-1</f>
+        <v>-0.15003798429982274</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20:T23" si="55">T3/P3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="T20:T23" si="49">T3/P3-1</f>
+        <v>-0.13983564013840832</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20:U23" si="56">U3/Q3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="U20:U23" si="50">U3/Q3-1</f>
+        <v>-0.12</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20:V23" si="57">V3/R3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="V20:V23" si="51">V3/R3-1</f>
+        <v>-0.10999999999999999</v>
       </c>
       <c r="X20" s="9"/>
       <c r="Y20" s="9">
@@ -3720,67 +3696,67 @@
         <v>0.34394518681152286</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20:AO23" si="58">Z3/Y3-1</f>
+        <f t="shared" ref="Z20:AO23" si="52">Z3/Y3-1</f>
         <v>0.26994901839281193</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.50482400691995477</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.31269897417757342</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.3563280337734795E-2</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.7292183622828583E-2</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
+        <v>-0.1303026145285463</v>
+      </c>
+      <c r="AF20" s="9">
+        <f t="shared" si="52"/>
+        <v>-5.0000000000000044E-2</v>
+      </c>
+      <c r="AG20" s="9">
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="58"/>
+      <c r="AH20" s="9">
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG20" s="9">
-        <f t="shared" si="58"/>
+      <c r="AI20" s="9">
+        <f t="shared" si="52"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="58"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AI20" s="9">
-        <f t="shared" si="58"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO20" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3789,130 +3765,130 @@
         <v>42</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>1.0255707762557078</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>1.0469107551487413</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.15284039675383232</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="44"/>
+        <v>-9.3782994845039713E-3</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="44"/>
+        <v>-3.4763139288239708E-3</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" si="44"/>
+        <v>0.13495602626037395</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" ref="O21:O23" si="53">O4/K4-1</f>
+        <v>0.19410767826880448</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" si="45"/>
+        <v>0.32482758620689656</v>
+      </c>
+      <c r="Q21" s="9">
+        <f t="shared" si="46"/>
+        <v>0.44551528410098751</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" si="47"/>
+        <v>0.50668485675306973</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" si="48"/>
+        <v>0.47232532751091716</v>
+      </c>
+      <c r="T21" s="9">
+        <f t="shared" si="49"/>
+        <v>0.37347972173583854</v>
+      </c>
+      <c r="U21" s="9">
         <f t="shared" si="50"/>
-        <v>0.15284039675383232</v>
-      </c>
-      <c r="L21" s="9">
-        <f t="shared" si="50"/>
-        <v>-9.3782994845039713E-3</v>
-      </c>
-      <c r="M21" s="9">
-        <f t="shared" si="50"/>
-        <v>-3.4763139288239708E-3</v>
-      </c>
-      <c r="N21" s="9">
-        <f t="shared" si="50"/>
-        <v>0.13495602626037395</v>
-      </c>
-      <c r="O21" s="9">
-        <f t="shared" ref="O21:O23" si="59">O4/K4-1</f>
-        <v>0.19410767826880448</v>
-      </c>
-      <c r="P21" s="9">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="V21" s="9">
         <f t="shared" si="51"/>
-        <v>0.32482758620689656</v>
-      </c>
-      <c r="Q21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.44551528410098751</v>
-      </c>
-      <c r="R21" s="9">
-        <f t="shared" si="53"/>
-        <v>0.50668485675306973</v>
-      </c>
-      <c r="S21" s="9">
-        <f t="shared" si="54"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="T21" s="9">
-        <f t="shared" si="55"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="U21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="V21" s="9">
-        <f t="shared" si="57"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="X21" s="9"/>
       <c r="Y21" s="9">
-        <f t="shared" ref="Y21:AN23" si="60">Y4/X4-1</f>
+        <f t="shared" ref="Y21:AN23" si="54">Y4/X4-1</f>
         <v>0.43548957228702712</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>7.2346712632356702E-2</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>0.61403508771929816</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>0.77916571818802627</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>6.4020343211732555E-2</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>0.37545468209830157</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="60"/>
-        <v>0.31293971084811312</v>
+        <f t="shared" si="54"/>
+        <v>0.32129517315236766</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="60"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="54"/>
+        <v>0.15999999999999992</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO21" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR21" t="s">
@@ -3927,137 +3903,137 @@
         <v>43</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>0.65079365079365092</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>0.28366762177650418</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9">
+        <f t="shared" si="44"/>
+        <v>0.55048076923076916</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="44"/>
+        <v>0.44866071428571441</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="44"/>
+        <v>0.42299349240780892</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="44"/>
+        <v>0.68822170900692825</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" si="53"/>
+        <v>0.62945736434108523</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="45"/>
+        <v>1.0292758089368257</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="46"/>
+        <v>0.93292682926829285</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="47"/>
+        <v>0.53214774281805699</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" si="48"/>
+        <v>0.32159847764034266</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" si="49"/>
+        <v>0.26955201214882307</v>
+      </c>
+      <c r="U22" s="9">
         <f t="shared" si="50"/>
-        <v>0.55048076923076916</v>
-      </c>
-      <c r="L22" s="9">
-        <f t="shared" si="50"/>
-        <v>0.44866071428571441</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" si="50"/>
-        <v>0.42299349240780892</v>
-      </c>
-      <c r="N22" s="9">
-        <f t="shared" si="50"/>
-        <v>0.68822170900692825</v>
-      </c>
-      <c r="O22" s="9">
-        <f t="shared" si="59"/>
-        <v>0.62945736434108523</v>
-      </c>
-      <c r="P22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V22" s="9">
         <f t="shared" si="51"/>
-        <v>1.0292758089368257</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" si="52"/>
-        <v>0.93292682926829285</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" si="53"/>
-        <v>0.53214774281805699</v>
-      </c>
-      <c r="S22" s="9">
-        <f t="shared" si="54"/>
-        <v>0.49999999999999978</v>
-      </c>
-      <c r="T22" s="9">
-        <f t="shared" si="55"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="U22" s="9">
-        <f t="shared" si="56"/>
-        <v>0.5</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="57"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="X22" s="9"/>
       <c r="Y22" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>-0.54597701149425282</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>1.7405063291139111E-2</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.16251944012441677</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.17591973244147163</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.52502844141069405</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.77396493845579983</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="58"/>
-        <v>0.42521026072329704</v>
+        <f t="shared" si="52"/>
+        <v>0.29100925147182521</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="58"/>
-        <v>0.35000000000000009</v>
+        <f t="shared" si="52"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="58"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="52"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="58"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="52"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="58"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="52"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="58"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="52"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="58"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="58"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="58"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="58"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR22" t="s">
         <v>56</v>
       </c>
       <c r="AS22" s="9">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="23" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4065,138 +4041,138 @@
         <v>44</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>0.65779798761609909</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="44"/>
         <v>0.65032072923700213</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9">
+        <f t="shared" si="44"/>
+        <v>9.4163991829588678E-2</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="44"/>
+        <v>-2.1659080448013013E-2</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="44"/>
+        <v>-2.2798235614808204E-3</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="44"/>
+        <v>9.7074635907014706E-2</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" si="53"/>
+        <v>0.14849187935034802</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="45"/>
+        <v>0.19104001672809012</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="46"/>
+        <v>0.20001490238934982</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="47"/>
+        <v>0.17680892672265025</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" si="48"/>
+        <v>0.12622779519331262</v>
+      </c>
+      <c r="T23" s="9">
+        <f t="shared" si="49"/>
+        <v>0.110033356741573</v>
+      </c>
+      <c r="U23" s="9">
         <f t="shared" si="50"/>
-        <v>9.4163991829588678E-2</v>
-      </c>
-      <c r="L23" s="9">
-        <f t="shared" si="50"/>
-        <v>-2.1659080448013013E-2</v>
-      </c>
-      <c r="M23" s="9">
-        <f t="shared" si="50"/>
-        <v>-2.2798235614808204E-3</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="50"/>
-        <v>9.7074635907014706E-2</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" si="59"/>
-        <v>0.14849187935034802</v>
-      </c>
-      <c r="P23" s="9">
+        <v>0.10302307771913477</v>
+      </c>
+      <c r="V23" s="9">
         <f t="shared" si="51"/>
-        <v>0.19104001672809012</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="52"/>
-        <v>0.20001490238934982</v>
-      </c>
-      <c r="R23" s="9">
-        <f t="shared" si="53"/>
-        <v>0.17680892672265025</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" si="54"/>
-        <v>0.19336769998838954</v>
-      </c>
-      <c r="T23" s="9">
-        <f t="shared" si="55"/>
-        <v>0.20719803370786516</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="56"/>
-        <v>0.17428086515574837</v>
-      </c>
-      <c r="V23" s="9">
-        <f t="shared" si="57"/>
-        <v>0.12329227761485839</v>
+        <v>6.6310850439882829E-2</v>
       </c>
       <c r="X23" s="9"/>
       <c r="Y23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>0.3166612836247864</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.1940531258760867</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.53325898425462603</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.46763712232143684</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>4.0000260842914193E-2</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.17942351222387298</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="58"/>
-        <v>0.17275973162925728</v>
+        <f t="shared" si="52"/>
+        <v>0.10005082457017123</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="58"/>
-        <v>0.10094423432467003</v>
+        <f t="shared" si="52"/>
+        <v>8.0130183373690933E-2</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="58"/>
-        <v>6.4684978098139778E-2</v>
+        <f t="shared" si="52"/>
+        <v>6.1938734345553748E-2</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="58"/>
-        <v>4.5594129541901118E-2</v>
+        <f t="shared" si="52"/>
+        <v>4.2002773201497368E-2</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="58"/>
-        <v>3.8454658539143205E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.3993075170032361E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="58"/>
-        <v>2.6285614412488556E-2</v>
+        <f t="shared" si="52"/>
+        <v>2.4085301814737781E-2</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="58"/>
-        <v>1.9551054251841338E-2</v>
+        <f t="shared" si="52"/>
+        <v>1.7283262345337613E-2</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="58"/>
-        <v>1.2606991977209381E-2</v>
+        <f t="shared" si="52"/>
+        <v>1.0787038179596475E-2</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="58"/>
-        <v>1.2027446184272872E-2</v>
+        <f t="shared" si="52"/>
+        <v>1.080199814042393E-2</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="58"/>
-        <v>1.1388990018398992E-2</v>
+        <f t="shared" si="52"/>
+        <v>1.0817230363766805E-2</v>
       </c>
       <c r="AO23" s="9">
-        <f t="shared" si="58"/>
-        <v>1.0707274714808257E-2</v>
+        <f t="shared" si="52"/>
+        <v>1.0832739341390951E-2</v>
       </c>
       <c r="AR23" t="s">
         <v>57</v>
       </c>
       <c r="AS23" s="4">
-        <f>NPV(AS22,AD16:ET16)</f>
-        <v>18352.796335391762</v>
+        <f>NPV(AS22,AE16:ET16)</f>
+        <v>17815.491630792279</v>
       </c>
     </row>
     <row r="24" spans="2:45" x14ac:dyDescent="0.3">
@@ -4204,78 +4180,78 @@
         <v>45</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:D24" si="61">C8/C6</f>
+        <f t="shared" ref="C24:D24" si="55">C8/C6</f>
         <v>0.445578560371517</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>0.45345205941931127</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9">
-        <f t="shared" ref="G24:N24" si="62">G8/G6</f>
+        <f t="shared" ref="G24:N24" si="56">G8/G6</f>
         <v>0.49244236941931707</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.51406433795325523</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.53853397432720418</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.50301622958681447</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.48547883830706456</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.49656290023262506</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.4949828622522478</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.48374554239042905</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" ref="O24:P24" si="63">O8/O6</f>
+        <f t="shared" ref="O24:P24" si="57">O8/O6</f>
         <v>0.49594798560315806</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="57"/>
         <v>0.48819346910112366</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:R24" si="64">Q8/Q6</f>
+        <f t="shared" ref="Q24:R24" si="58">Q8/Q6</f>
         <v>0.49179343889061378</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="64"/>
-        <v>0.48</v>
+        <f t="shared" si="58"/>
+        <v>0.4946236559139785</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:V24" si="65">S8/S6</f>
-        <v>0.5</v>
+        <f t="shared" ref="S24:V24" si="59">S8/S6</f>
+        <v>0.51337085833281793</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="65"/>
-        <v>0.5</v>
+        <f t="shared" si="59"/>
+        <v>0.52338776639911422</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="65"/>
-        <v>0.49</v>
+        <f t="shared" si="59"/>
+        <v>0.51</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="65"/>
-        <v>0.48</v>
+        <f t="shared" si="59"/>
+        <v>0.52</v>
       </c>
       <c r="X24" s="9">
         <f>X8/X6</f>
@@ -4286,75 +4262,75 @@
         <v>0.51603238015138764</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AO24" si="66">Z8/Z6</f>
+        <f t="shared" ref="Z24:AO24" si="60">Z8/Z6</f>
         <v>0.44644665209033418</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>0.44721352895575534</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>0.51281716868059124</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>0.49006477179385893</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>0.49264213335601648</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49221881072247919</v>
+        <f t="shared" si="60"/>
+        <v>0.51669875161755396</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49</v>
+        <f t="shared" si="60"/>
+        <v>0.53</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49000000000000005</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.48999999999999994</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49000000000000005</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.49</v>
+        <f t="shared" si="60"/>
+        <v>0.54</v>
       </c>
       <c r="AR24" t="s">
         <v>58</v>
       </c>
       <c r="AS24" s="4">
         <f>AS23/Main!D13</f>
-        <v>3219.7888307704843</v>
+        <v>3158.7751118426031</v>
       </c>
     </row>
     <row r="25" spans="2:45" x14ac:dyDescent="0.3">
@@ -4362,77 +4338,77 @@
         <v>46</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:D25" si="67">C9/C6</f>
+        <f t="shared" ref="C25:D25" si="61">C9/C6</f>
         <v>0.1780669504643963</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>0.15352802160702228</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9">
-        <f t="shared" ref="G25:N25" si="68">G9/G6</f>
+        <f t="shared" ref="G25:N25" si="62">G9/G6</f>
         <v>0.14026845637583893</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.1276274740449036</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.13153590722109332</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.10992200711779701</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>8.478011574259274E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>8.4006377584359221E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>9.3934727534648044E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>9.4857931669159068E-2</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25:P25" si="69">O9/O6</f>
+        <f t="shared" ref="O25:P25" si="63">O9/O6</f>
         <v>0.10156739811912226</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>0.10255003511235955</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25:R25" si="70">Q9/Q6</f>
+        <f t="shared" ref="Q25:R25" si="64">Q9/Q6</f>
         <v>0.1007968539790955</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>9.1495601173020524E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="71">S9/S6</f>
-        <v>9.9999999999999992E-2</v>
+        <f t="shared" ref="S25:V25" si="65">S9/S6</f>
+        <v>8.7235314735778641E-2</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="71"/>
-        <v>0.1</v>
+        <f t="shared" si="65"/>
+        <v>8.9438930844964612E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="71"/>
-        <v>0.1</v>
+        <f t="shared" si="65"/>
+        <v>0.09</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.09</v>
       </c>
       <c r="X25" s="9">
@@ -4444,75 +4420,75 @@
         <v>9.9032800672834348E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AO25" si="72">Z9/Z6</f>
+        <f t="shared" ref="Z25:AO25" si="66">Z9/Z6</f>
         <v>9.0612939674527118E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.14584589470460441</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.12690659867361379</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>8.9652188634525301E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>9.8868674839711235E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="72"/>
-        <v>9.73953751003655E-2</v>
+        <f t="shared" si="66"/>
+        <v>8.9214807302780197E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="72"/>
-        <v>9.9999999999999992E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>8.9999999999999983E-2</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AO25" s="9">
-        <f t="shared" si="72"/>
-        <v>0.1</v>
+        <f t="shared" si="66"/>
+        <v>0.09</v>
       </c>
       <c r="AR25" t="s">
         <v>59</v>
       </c>
       <c r="AS25" s="4">
         <f>Main!D10</f>
-        <v>-1781.8596491228072</v>
+        <v>-331.968085106383</v>
       </c>
     </row>
     <row r="26" spans="2:45" x14ac:dyDescent="0.3">
@@ -4524,29 +4500,29 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9">
-        <f t="shared" ref="G26:N27" si="73">G10/C10-1</f>
+        <f t="shared" ref="G26:N27" si="67">G10/C10-1</f>
         <v>-0.12585933368588043</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="67"/>
         <v>-9.7388224878264706E-2</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="67"/>
         <v>3.6902601330913498E-2</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="67"/>
         <v>-2.4521824423736627E-3</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="67"/>
         <v>0.11332973556395043</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="67"/>
         <v>0.32749562171628832</v>
       </c>
       <c r="O26" s="9">
@@ -4554,32 +4530,32 @@
         <v>0.34539089848308047</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" ref="P26:P27" si="74">P10/L10-1</f>
+        <f t="shared" ref="P26:P27" si="68">P10/L10-1</f>
         <v>6.2930186823991985E-2</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" ref="Q26:Q27" si="75">Q10/M10-1</f>
+        <f t="shared" ref="Q26:Q27" si="69">Q10/M10-1</f>
         <v>0.30150266602035858</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" ref="R26:R27" si="76">R10/N10-1</f>
+        <f t="shared" ref="R26:R27" si="70">R10/N10-1</f>
         <v>0.69525065963060562</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:S27" si="77">S10/O10-1</f>
-        <v>0.30000000000000027</v>
+        <f t="shared" ref="S26:S27" si="71">S10/O10-1</f>
+        <v>5.3339115351257682E-2</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" ref="T26:T27" si="78">T10/P10-1</f>
-        <v>0.49999999999999978</v>
+        <f t="shared" ref="T26:T27" si="72">T10/P10-1</f>
+        <v>4.8566142460684469E-2</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" ref="U26:U27" si="79">U10/Q10-1</f>
-        <v>0.30000000000000004</v>
+        <f t="shared" ref="U26:U27" si="73">U10/Q10-1</f>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" ref="V26:V27" si="80">V10/R10-1</f>
-        <v>0.30000000000000004</v>
+        <f t="shared" ref="V26:V27" si="74">V10/R10-1</f>
+        <v>0.14999999999999991</v>
       </c>
       <c r="X26" s="9"/>
       <c r="Y26" s="9">
@@ -4587,75 +4563,75 @@
         <v>-0.2652570053292076</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AO26" si="81">Z10/Y10-1</f>
+        <f t="shared" ref="Z26:AO26" si="75">Z10/Y10-1</f>
         <v>0.31937295273748245</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="75"/>
         <v>0.55630430927469421</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="75"/>
         <v>-0.23803555150410205</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="75"/>
         <v>9.570809032451022E-2</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="75"/>
         <v>0.32700969018697945</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="81"/>
-        <v>0.34447187082176289</v>
+        <f t="shared" si="75"/>
+        <v>7.6905276149336732E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="81"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="75"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="81"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="75"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="81"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="75"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="81"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="75"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="81"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="75"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="81"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="75"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="81"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="75"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="81"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="75"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="81"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="75"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO26" s="9">
-        <f t="shared" si="81"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="75"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR26" t="s">
         <v>60</v>
       </c>
       <c r="AS26" s="4">
         <f>AS24+AS25</f>
-        <v>1437.9291816476771</v>
+        <v>2826.80702673622</v>
       </c>
     </row>
     <row r="27" spans="2:45" x14ac:dyDescent="0.3">
@@ -4667,62 +4643,62 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="67"/>
         <v>12.977477477477478</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="67"/>
         <v>4.6472346786248124</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9">
+        <f t="shared" si="67"/>
+        <v>0.31002255881405083</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="67"/>
+        <v>5.2938062466913793E-2</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="67"/>
+        <v>-0.10948191593352885</v>
+      </c>
+      <c r="N27" s="9">
+        <f t="shared" si="67"/>
+        <v>-1.5912015912015631E-2</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" ref="O27" si="76">O11/K11-1</f>
+        <v>1.7343173431734416E-2</v>
+      </c>
+      <c r="P27" s="9">
+        <f t="shared" si="68"/>
+        <v>8.5218702865761609E-2</v>
+      </c>
+      <c r="Q27" s="9">
+        <f t="shared" si="69"/>
+        <v>0.17611903890718383</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="70"/>
+        <v>0.29829984544049482</v>
+      </c>
+      <c r="S27" s="9">
+        <f t="shared" si="71"/>
+        <v>0.42401160681900607</v>
+      </c>
+      <c r="T27" s="9">
+        <f t="shared" si="72"/>
+        <v>0.48193189715079932</v>
+      </c>
+      <c r="U27" s="9">
         <f t="shared" si="73"/>
-        <v>0.31002255881405083</v>
-      </c>
-      <c r="L27" s="9">
-        <f t="shared" si="73"/>
-        <v>5.2938062466913793E-2</v>
-      </c>
-      <c r="M27" s="9">
-        <f t="shared" si="73"/>
-        <v>-0.10948191593352885</v>
-      </c>
-      <c r="N27" s="9">
-        <f t="shared" si="73"/>
-        <v>-1.5912015912015631E-2</v>
-      </c>
-      <c r="O27" s="9">
-        <f t="shared" ref="O27" si="82">O11/K11-1</f>
-        <v>1.7343173431734416E-2</v>
-      </c>
-      <c r="P27" s="9">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="V27" s="9">
         <f t="shared" si="74"/>
-        <v>8.5218702865761609E-2</v>
-      </c>
-      <c r="Q27" s="9">
-        <f t="shared" si="75"/>
-        <v>0.17611903890718383</v>
-      </c>
-      <c r="R27" s="9">
-        <f t="shared" si="76"/>
-        <v>0.29829984544049482</v>
-      </c>
-      <c r="S27" s="9">
-        <f t="shared" si="77"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="T27" s="9">
-        <f t="shared" si="78"/>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="U27" s="9">
-        <f t="shared" si="79"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="V27" s="9">
-        <f t="shared" si="80"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="X27" s="9"/>
       <c r="Y27" s="9">
@@ -4730,75 +4706,75 @@
         <v>0.22115384615384626</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27:AO27" si="83">Z11/Y11-1</f>
+        <f t="shared" ref="Z27:AO27" si="77">Z11/Y11-1</f>
         <v>1.8661417322834644</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>6.23992673992674</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>2.9863394889956991</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>3.7441299657317018E-2</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>0.1459505749938832</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="83"/>
-        <v>9.5118501120956322E-2</v>
+        <f t="shared" si="77"/>
+        <v>0.39503576385182027</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="83"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="77"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="83"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="77"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="77"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL27" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="77"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM27" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="77"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN27" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="77"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO27" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="77"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR27" t="s">
         <v>61</v>
       </c>
       <c r="AS27" s="10">
         <f>AS26/AO17</f>
-        <v>4.5489692554497845</v>
+        <v>9.4954888368700701</v>
       </c>
     </row>
     <row r="28" spans="2:45" x14ac:dyDescent="0.3">
@@ -4806,78 +4782,78 @@
         <v>49</v>
       </c>
       <c r="C28" s="9">
-        <f t="shared" ref="C28:D28" si="84">C12/C6</f>
+        <f t="shared" ref="C28:D28" si="78">C12/C6</f>
         <v>0.15455688854489161</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="78"/>
         <v>0.14812626603646187</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9">
-        <f t="shared" ref="G28:N28" si="85">G12/G6</f>
+        <f t="shared" ref="G28:N28" si="79">G12/G6</f>
         <v>0.12284797198716066</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.1410780954329259</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.13292362591069035</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.14853984199500253</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.13817105368429472</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.1514414908910322</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.14616760220555367</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.16049695157022897</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28:P28" si="86">O12/O6</f>
+        <f t="shared" ref="O28:P28" si="80">O12/O6</f>
         <v>0.14877510739579711</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="80"/>
         <v>0.14872278792134838</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" ref="Q28:R28" si="87">Q12/Q6</f>
+        <f t="shared" ref="Q28:R28" si="81">Q12/Q6</f>
         <v>0.13583773155334797</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="87"/>
-        <v>0.12477028347996086</v>
+        <f t="shared" si="81"/>
+        <v>0.1393939393939394</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" ref="S28:V28" si="88">S12/S6</f>
-        <v>0.15658940099680144</v>
+        <f t="shared" ref="S28:V28" si="82">S12/S6</f>
+        <v>0.13321374817014092</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.1605490677990751</v>
+        <f t="shared" si="82"/>
+        <v>0.1361749238859673</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.1500148267271674</v>
+        <f t="shared" si="82"/>
+        <v>0.11377620440827015</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="88"/>
-        <v>0.13229154628553128</v>
+        <f t="shared" si="82"/>
+        <v>0.11553476416253218</v>
       </c>
       <c r="X28" s="9">
         <f>X12/X6</f>
@@ -4888,75 +4864,75 @@
         <v>0.3354359405663021</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28:AO28" si="89">Z12/Z6</f>
+        <f t="shared" ref="Z28:AO28" si="83">Z12/Z6</f>
         <v>0.25706193963050467</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="83"/>
         <v>0.14171140907481325</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="83"/>
         <v>0.13678602403667445</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="83"/>
         <v>0.1494579359555564</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="83"/>
         <v>0.14288828164042131</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.1495572050632801</v>
+        <f t="shared" si="83"/>
+        <v>0.1242713477496523</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.14800910241044204</v>
+        <f t="shared" si="83"/>
+        <v>0.12840617437086124</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.14997969086100457</v>
+        <f t="shared" si="83"/>
+        <v>0.13991031631504672</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.15228290820263046</v>
+        <f t="shared" si="83"/>
+        <v>0.14348222249525686</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.15521677390108954</v>
+        <f t="shared" si="83"/>
+        <v>0.14763034147648868</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.15600077489294958</v>
+        <f t="shared" si="83"/>
+        <v>0.14883656063860218</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.15589773644603111</v>
+        <f t="shared" si="83"/>
+        <v>0.15099274704103666</v>
       </c>
       <c r="AL28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.15418856405603149</v>
+        <f t="shared" si="83"/>
+        <v>0.15122556574088744</v>
       </c>
       <c r="AM28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.15233088779387521</v>
+        <f t="shared" si="83"/>
+        <v>0.15146262160457077</v>
       </c>
       <c r="AN28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.15030736260453337</v>
+        <f t="shared" si="83"/>
+        <v>0.15170398453647915</v>
       </c>
       <c r="AO28" s="9">
-        <f t="shared" si="89"/>
-        <v>0.1481035614764297</v>
+        <f t="shared" si="83"/>
+        <v>0.15194972531810291</v>
       </c>
       <c r="AR28" t="s">
         <v>62</v>
       </c>
       <c r="AS28" s="10">
         <f>Main!D3</f>
-        <v>8.5</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="29" spans="2:45" x14ac:dyDescent="0.3">
@@ -4964,78 +4940,78 @@
         <v>27</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:D29" si="90">C15/C14</f>
+        <f t="shared" ref="C29:D29" si="84">C15/C14</f>
         <v>0.24701637524285325</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>0.19526627218934911</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9">
-        <f t="shared" ref="G29:N29" si="91">G15/G14</f>
+        <f t="shared" ref="G29:N29" si="85">G15/G14</f>
         <v>0.15990396158463402</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="85"/>
         <v>0.17122204653264059</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="85"/>
         <v>0.10580766517752178</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="85"/>
         <v>0.14135243311565182</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="85"/>
         <v>0.15186969488414778</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="85"/>
         <v>0.11930764475582112</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="85"/>
         <v>0.19777430691136264</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="85"/>
         <v>0.23650385604113086</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29:P29" si="92">O15/O14</f>
+        <f t="shared" ref="O29:P29" si="86">O15/O14</f>
         <v>0.15685589519650647</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="86"/>
         <v>0.12824506749740386</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" ref="Q29:R29" si="93">Q15/Q14</f>
+        <f t="shared" ref="Q29:R29" si="87">Q15/Q14</f>
         <v>0.10513900589721974</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="93"/>
-        <v>-6.5930149679258754E-2</v>
+        <f t="shared" si="87"/>
+        <v>-5.8176100628930819E-2</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" ref="S29:V29" si="94">S15/S14</f>
-        <v>0.18</v>
+        <f t="shared" ref="S29:V29" si="88">S15/S14</f>
+        <v>9.4499051560613806E-2</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="94"/>
-        <v>0.18</v>
+        <f t="shared" si="88"/>
+        <v>0.12901655306718604</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="94"/>
-        <v>0.18</v>
+        <f t="shared" si="88"/>
+        <v>0.15</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="94"/>
-        <v>0.18</v>
+        <f t="shared" si="88"/>
+        <v>0.15</v>
       </c>
       <c r="X29" s="9">
         <f>X15/X14</f>
@@ -5046,67 +5022,67 @@
         <v>0.28522875816993482</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29:AO29" si="95">Z15/Z14</f>
+        <f t="shared" ref="Z29:AO29" si="89">Z15/Z14</f>
         <v>0.27182058939539067</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="89"/>
         <v>0.21619623655913961</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="89"/>
         <v>0.14466803092314701</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="89"/>
         <v>0.18017750012395256</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="89"/>
         <v>7.9544499537776411E-2</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="89"/>
+        <v>0.13029907433116683</v>
+      </c>
+      <c r="AF29" s="9">
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
-      <c r="AF29" s="9">
-        <f t="shared" si="95"/>
+      <c r="AG29" s="9">
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
-      <c r="AG29" s="9">
-        <f t="shared" si="95"/>
+      <c r="AH29" s="9">
+        <f t="shared" si="89"/>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="AI29" s="9">
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
-      <c r="AH29" s="9">
-        <f t="shared" si="95"/>
+      <c r="AJ29" s="9">
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
-      <c r="AI29" s="9">
-        <f t="shared" si="95"/>
+      <c r="AK29" s="9">
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
-      <c r="AJ29" s="9">
-        <f t="shared" si="95"/>
+      <c r="AL29" s="9">
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
-      <c r="AK29" s="9">
-        <f t="shared" si="95"/>
+      <c r="AM29" s="9">
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
-      <c r="AL29" s="9">
-        <f t="shared" si="95"/>
+      <c r="AN29" s="9">
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
-      <c r="AM29" s="9">
-        <f t="shared" si="95"/>
-        <v>0.18</v>
-      </c>
-      <c r="AN29" s="9">
-        <f t="shared" si="95"/>
-        <v>0.18</v>
-      </c>
       <c r="AO29" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="89"/>
         <v>0.18</v>
       </c>
       <c r="AR29" s="1" t="s">
@@ -5114,7 +5090,7 @@
       </c>
       <c r="AS29" s="11">
         <f>AS27/AS28-1</f>
-        <v>-0.46482714641767242</v>
+        <v>-0.11090928493725938</v>
       </c>
     </row>
     <row r="30" spans="2:45" x14ac:dyDescent="0.3">
@@ -5122,78 +5098,78 @@
         <v>50</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:D30" si="96">C16/C6</f>
+        <f t="shared" ref="C30:D30" si="90">C16/C6</f>
         <v>0.13124032507739936</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="90"/>
         <v>0.11478730587440919</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9">
-        <f t="shared" ref="G30:N30" si="97">G16/G6</f>
+        <f t="shared" ref="G30:N30" si="91">G16/G6</f>
         <v>0.10210096294134799</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="91"/>
         <v>9.3821919909988241E-2</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="91"/>
         <v>9.4240967438172132E-2</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="91"/>
         <v>0.10287993134607146</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="91"/>
         <v>9.8594554231005133E-2</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="91"/>
         <v>0.11171227684989155</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="91"/>
         <v>0.10205652973026681</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="91"/>
         <v>0.10249626135971478</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" ref="O30:P30" si="98">O16/O6</f>
+        <f t="shared" ref="O30:P30" si="92">O16/O6</f>
         <v>0.11208638105189835</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="92"/>
         <v>0.11053809691011242</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" ref="Q30:R30" si="99">Q16/Q6</f>
+        <f t="shared" ref="Q30:R30" si="93">Q16/Q6</f>
         <v>0.10992445410328072</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="99"/>
-        <v>0.11695014662756595</v>
+        <f t="shared" si="93"/>
+        <v>0.13157380254154447</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" ref="S30:V30" si="100">S16/S6</f>
-        <v>0.11730390458663326</v>
+        <f t="shared" ref="S30:V30" si="94">S16/S6</f>
+        <v>0.10826580895239285</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="100"/>
-        <v>0.11646082138390393</v>
+        <f t="shared" si="94"/>
+        <v>0.10610493851567745</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="100"/>
-        <v>0.11375410412338822</v>
+        <f t="shared" si="94"/>
+        <v>8.6493038052591217E-2</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="100"/>
-        <v>9.727008166192104E-2</v>
+        <f t="shared" si="94"/>
+        <v>8.5964579460157134E-2</v>
       </c>
       <c r="X30" s="9">
         <f>X16/X6</f>
@@ -5204,79 +5180,74 @@
         <v>0.23952200728903825</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" ref="Z30:AO30" si="101">Z16/Z6</f>
+        <f t="shared" ref="Z30:AO30" si="95">Z16/Z6</f>
         <v>0.18963417318443959</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="95"/>
         <v>0.11162154143577679</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="95"/>
         <v>9.8122583127376026E-2</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="95"/>
         <v>0.10367876199971159</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="95"/>
         <v>0.11645525204946339</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11096261781838251</v>
+        <f t="shared" si="95"/>
+        <v>9.6251461549673706E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11044545842113275</v>
+        <f t="shared" si="95"/>
+        <v>9.4659079883269992E-2</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11241715467133848</v>
+        <f t="shared" si="95"/>
+        <v>0.10441230260110074</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11446337847805764</v>
+        <f t="shared" si="95"/>
+        <v>0.10746007387912521</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11695389081978147</v>
+        <f t="shared" si="95"/>
+        <v>0.11090090384785509</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11755940697526676</v>
+        <f t="shared" si="95"/>
+        <v>0.11183134679296458</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11736872761899296</v>
+        <f t="shared" si="95"/>
+        <v>0.11347172973393908</v>
       </c>
       <c r="AL30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11578741305556348</v>
+        <f t="shared" si="95"/>
+        <v>0.11346605499543148</v>
       </c>
       <c r="AM30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11407503516528195</v>
+        <f t="shared" si="95"/>
+        <v>0.11346027698001024</v>
       </c>
       <c r="AN30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11221634115885511</v>
+        <f t="shared" si="95"/>
+        <v>0.11345439398382098</v>
       </c>
       <c r="AO30" s="9">
-        <f t="shared" si="101"/>
-        <v>0.11019857110011112</v>
+        <f t="shared" si="95"/>
+        <v>0.11344840428163099</v>
       </c>
       <c r="AR30" t="s">
         <v>64</v>
       </c>
       <c r="AS30" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AS32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/PAGS.xlsx
+++ b/Financial Analysis/PAGS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62705682-10E6-4C05-9C71-F0D7FCD1C8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60023246-045D-4FDC-B4DC-523C5D3F5A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{59555B69-E0C6-4AC2-AD53-EB3ED27D9884}"/>
   </bookViews>
@@ -235,7 +235,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -768,14 +768,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="10">
-        <v>10.68</v>
+        <v>9.24</v>
       </c>
       <c r="E3" s="3">
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45980</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>3179.4359999999997</v>
+        <v>2750.748</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -859,7 +859,7 @@
       </c>
       <c r="D11" s="4">
         <f>D5-D10</f>
-        <v>3511.4040851063828</v>
+        <v>3082.7160851063832</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AS28" s="10">
         <f>Main!D3</f>
-        <v>10.68</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="29" spans="2:45" x14ac:dyDescent="0.3">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AS29" s="11">
         <f>AS27/AS28-1</f>
-        <v>-0.11090928493725938</v>
+        <v>2.7650307020570253E-2</v>
       </c>
     </row>
     <row r="30" spans="2:45" x14ac:dyDescent="0.3">
